--- a/strategy_grp2/app/control/control_board.xlsx
+++ b/strategy_grp2/app/control/control_board.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\Gandalf\sm-home\potentials\strategy_grp2\app\control\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3400EC81-26C1-43BA-A31A-D7BF2B1BA3A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9098EDB7-00C0-4EA8-9E2F-681F232E7EB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="29505" yWindow="1485" windowWidth="35205" windowHeight="14355" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="25920" yWindow="1020" windowWidth="28935" windowHeight="14355" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Runs" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="821" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="828" uniqueCount="164">
   <si>
     <t>D</t>
   </si>
@@ -502,6 +502,18 @@
   </si>
   <si>
     <t>Rimelig</t>
+  </si>
+  <si>
+    <t>Mindre god</t>
+  </si>
+  <si>
+    <t>Mindre god, men mild i extention</t>
+  </si>
+  <si>
+    <t>God (basis)</t>
+  </si>
+  <si>
+    <t>rank, per1d,per5d,per10d</t>
   </si>
 </sst>
 </file>
@@ -530,7 +542,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -575,12 +587,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -630,7 +636,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -645,8 +651,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -950,14 +954,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Y81"/>
+  <dimension ref="A1:Y82"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="3" width="4.42578125" customWidth="1"/>
     <col min="4" max="4" width="15.42578125" customWidth="1"/>
     <col min="5" max="5" width="43.140625" customWidth="1"/>
-    <col min="6" max="15" width="18" customWidth="1"/>
+    <col min="6" max="6" width="30.42578125" customWidth="1"/>
+    <col min="7" max="15" width="18" customWidth="1"/>
     <col min="16" max="16" width="27.85546875" customWidth="1"/>
     <col min="17" max="25" width="18" customWidth="1"/>
   </cols>
@@ -1040,6 +1045,9 @@
       </c>
     </row>
     <row r="2" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>23</v>
+      </c>
       <c r="B2" t="s">
         <v>23</v>
       </c>
@@ -1054,7 +1062,7 @@
         <v>01 GICS-beta3m (beta3m+ Longi.beta3m&gt;2.5)</v>
       </c>
       <c r="F2" t="s">
-        <v>30</v>
+        <v>162</v>
       </c>
       <c r="G2" t="s">
         <v>25</v>
@@ -1102,26 +1110,20 @@
         <v>0</v>
       </c>
       <c r="X2" t="s">
-        <v>135</v>
+        <v>163</v>
       </c>
     </row>
     <row r="3" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>23</v>
-      </c>
       <c r="C3">
         <f>C2+1</f>
         <v>2</v>
       </c>
-      <c r="D3" t="s">
-        <v>157</v>
-      </c>
       <c r="E3" t="str">
-        <f t="shared" ref="E3:E10" si="0">TEXT(C3,"00") &amp; " GICS-"&amp;K3&amp;" ("&amp;Q3&amp;IF(P3&lt;&gt;"","+ ","")&amp;P3&amp;")"</f>
-        <v>02 GICS-beta3m (beta3m+ Longi.beta3m&gt;2.5)</v>
+        <f t="shared" ref="E3" si="0">TEXT(C3,"00") &amp; " GICS-"&amp;K3&amp;" ("&amp;Q3&amp;IF(P3&lt;&gt;"","+ ","")&amp;P3&amp;")"</f>
+        <v>02 GICS-beta3m (beta3m)</v>
       </c>
       <c r="F3" t="s">
-        <v>30</v>
+        <v>159</v>
       </c>
       <c r="G3" t="s">
         <v>25</v>
@@ -1144,9 +1146,6 @@
       <c r="O3">
         <v>4</v>
       </c>
-      <c r="P3" t="s">
-        <v>143</v>
-      </c>
       <c r="Q3" t="s">
         <v>27</v>
       </c>
@@ -1157,7 +1156,7 @@
         <v>1</v>
       </c>
       <c r="T3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="U3">
         <v>0</v>
@@ -1169,20 +1168,20 @@
         <v>0</v>
       </c>
       <c r="X3" t="s">
-        <v>135</v>
+        <v>148</v>
       </c>
     </row>
     <row r="4" spans="1:25" x14ac:dyDescent="0.25">
       <c r="C4">
-        <f t="shared" ref="C4:C6" si="1">C3+1</f>
+        <f t="shared" ref="C4:C5" si="1">C3+1</f>
         <v>3</v>
       </c>
       <c r="E4" t="str">
-        <f t="shared" ref="E4" si="2">TEXT(C4,"00") &amp; " GICS-"&amp;K4&amp;" ("&amp;Q4&amp;IF(P4&lt;&gt;"","+ ","")&amp;P4&amp;")"</f>
-        <v>03 GICS-beta3m (beta3m)</v>
+        <f t="shared" ref="E4:E9" si="2">TEXT(C4,"00") &amp; " GICS-"&amp;K4&amp;" ("&amp;Q4&amp;IF(P4&lt;&gt;"","+ ","")&amp;P4&amp;")"</f>
+        <v>03 GICS-rank (beta3m+ Longi.beta3m&gt;2.5)</v>
       </c>
       <c r="F4" t="s">
-        <v>159</v>
+        <v>30</v>
       </c>
       <c r="G4" t="s">
         <v>25</v>
@@ -1191,10 +1190,10 @@
         <v>26</v>
       </c>
       <c r="K4" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="L4" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="M4">
         <v>0.1</v>
@@ -1205,6 +1204,9 @@
       <c r="O4">
         <v>4</v>
       </c>
+      <c r="P4" t="s">
+        <v>143</v>
+      </c>
       <c r="Q4" t="s">
         <v>27</v>
       </c>
@@ -1215,7 +1217,7 @@
         <v>1</v>
       </c>
       <c r="T4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="U4">
         <v>0</v>
@@ -1227,7 +1229,7 @@
         <v>0</v>
       </c>
       <c r="X4" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
     </row>
     <row r="5" spans="1:25" x14ac:dyDescent="0.25">
@@ -1236,8 +1238,8 @@
         <v>4</v>
       </c>
       <c r="E5" t="str">
-        <f t="shared" si="0"/>
-        <v>04 GICS-rank (beta3m+ Longi.beta3m&gt;2.5)</v>
+        <f t="shared" si="2"/>
+        <v>04 GICS-rank (beta3m+ Longi.beta3m&gt;3)</v>
       </c>
       <c r="F5" t="s">
         <v>30</v>
@@ -1264,7 +1266,7 @@
         <v>4</v>
       </c>
       <c r="P5" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="Q5" t="s">
         <v>27</v>
@@ -1287,18 +1289,18 @@
       <c r="W5">
         <v>0</v>
       </c>
-      <c r="X5" t="s">
-        <v>142</v>
+      <c r="X5" s="10" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="6" spans="1:25" x14ac:dyDescent="0.25">
       <c r="C6">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="C6:C69" si="3">C5+1</f>
         <v>5</v>
       </c>
       <c r="E6" t="str">
-        <f t="shared" si="0"/>
-        <v>05 GICS-rank (beta3m+ Longi.beta3m&gt;3)</v>
+        <f t="shared" si="2"/>
+        <v>05 GICS-PdivMA20 (beta3m)</v>
       </c>
       <c r="F6" t="s">
         <v>30</v>
@@ -1310,10 +1312,10 @@
         <v>26</v>
       </c>
       <c r="K6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L6" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="M6">
         <v>0.1</v>
@@ -1324,9 +1326,6 @@
       <c r="O6">
         <v>4</v>
       </c>
-      <c r="P6" t="s">
-        <v>144</v>
-      </c>
       <c r="Q6" t="s">
         <v>27</v>
       </c>
@@ -1348,21 +1347,24 @@
       <c r="W6">
         <v>0</v>
       </c>
-      <c r="X6" s="10" t="s">
-        <v>135</v>
+      <c r="X6" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="7" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>23</v>
+      </c>
       <c r="C7">
-        <f t="shared" ref="C7:C70" si="3">C6+1</f>
+        <f t="shared" si="3"/>
         <v>6</v>
       </c>
       <c r="E7" t="str">
-        <f t="shared" si="0"/>
-        <v>06 GICS-PdivMA20 (beta3m)</v>
+        <f t="shared" si="2"/>
+        <v>06 GICS-sh3m (beta3m)</v>
       </c>
       <c r="F7" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="G7" t="s">
         <v>25</v>
@@ -1371,7 +1373,7 @@
         <v>26</v>
       </c>
       <c r="K7" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="L7" t="s">
         <v>28</v>
@@ -1407,23 +1409,20 @@
         <v>0</v>
       </c>
       <c r="X7" t="s">
-        <v>29</v>
+        <v>163</v>
       </c>
     </row>
     <row r="8" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>23</v>
-      </c>
       <c r="C8">
         <f t="shared" si="3"/>
         <v>7</v>
       </c>
       <c r="E8" t="str">
-        <f t="shared" si="0"/>
-        <v>07 GICS-sh3m (beta3m)</v>
+        <f t="shared" si="2"/>
+        <v>07 GICS-quot1020 (beta3m)</v>
       </c>
       <c r="F8" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="G8" t="s">
         <v>25</v>
@@ -1432,7 +1431,7 @@
         <v>26</v>
       </c>
       <c r="K8" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="L8" t="s">
         <v>28</v>
@@ -1477,11 +1476,11 @@
         <v>8</v>
       </c>
       <c r="E9" t="str">
-        <f t="shared" si="0"/>
-        <v>08 GICS-quot1020 (beta3m)</v>
+        <f t="shared" si="2"/>
+        <v>08 GICS-quot2050 (beta3m)</v>
       </c>
       <c r="F9" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="G9" t="s">
         <v>25</v>
@@ -1490,7 +1489,7 @@
         <v>26</v>
       </c>
       <c r="K9" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="L9" t="s">
         <v>28</v>
@@ -1530,28 +1529,21 @@
       </c>
     </row>
     <row r="10" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>23</v>
-      </c>
       <c r="C10">
         <f t="shared" si="3"/>
         <v>9</v>
       </c>
-      <c r="E10" t="str">
-        <f t="shared" si="0"/>
-        <v>09 GICS-quot2050 (beta3m)</v>
-      </c>
-      <c r="F10" t="s">
-        <v>24</v>
+      <c r="E10" t="s">
+        <v>35</v>
       </c>
       <c r="G10" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="H10" t="s">
         <v>26</v>
       </c>
       <c r="K10" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="L10" t="s">
         <v>28</v>
@@ -1596,7 +1588,7 @@
         <v>10</v>
       </c>
       <c r="E11" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G11" t="s">
         <v>36</v>
@@ -1605,10 +1597,10 @@
         <v>26</v>
       </c>
       <c r="K11" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="L11" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="M11">
         <v>0.1</v>
@@ -1650,7 +1642,7 @@
         <v>11</v>
       </c>
       <c r="E12" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G12" t="s">
         <v>36</v>
@@ -1659,10 +1651,10 @@
         <v>26</v>
       </c>
       <c r="K12" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="L12" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="M12">
         <v>0.1</v>
@@ -1704,7 +1696,7 @@
         <v>12</v>
       </c>
       <c r="E13" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G13" t="s">
         <v>36</v>
@@ -1713,7 +1705,7 @@
         <v>26</v>
       </c>
       <c r="K13" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="L13" t="s">
         <v>28</v>
@@ -1758,7 +1750,7 @@
         <v>13</v>
       </c>
       <c r="E14" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G14" t="s">
         <v>36</v>
@@ -1767,7 +1759,7 @@
         <v>26</v>
       </c>
       <c r="K14" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L14" t="s">
         <v>28</v>
@@ -1812,7 +1804,7 @@
         <v>14</v>
       </c>
       <c r="E15" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G15" t="s">
         <v>36</v>
@@ -1821,7 +1813,7 @@
         <v>26</v>
       </c>
       <c r="K15" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="L15" t="s">
         <v>28</v>
@@ -1866,7 +1858,7 @@
         <v>15</v>
       </c>
       <c r="E16" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G16" t="s">
         <v>36</v>
@@ -1875,10 +1867,10 @@
         <v>26</v>
       </c>
       <c r="K16" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="L16" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="M16">
         <v>0.1</v>
@@ -1920,7 +1912,7 @@
         <v>16</v>
       </c>
       <c r="E17" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G17" t="s">
         <v>36</v>
@@ -1929,10 +1921,10 @@
         <v>26</v>
       </c>
       <c r="K17" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="L17" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="M17">
         <v>0.1</v>
@@ -1974,7 +1966,7 @@
         <v>17</v>
       </c>
       <c r="E18" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G18" t="s">
         <v>36</v>
@@ -1983,7 +1975,7 @@
         <v>26</v>
       </c>
       <c r="K18" t="s">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="L18" t="s">
         <v>28</v>
@@ -2028,7 +2020,7 @@
         <v>18</v>
       </c>
       <c r="E19" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G19" t="s">
         <v>36</v>
@@ -2037,10 +2029,10 @@
         <v>26</v>
       </c>
       <c r="K19" t="s">
-        <v>34</v>
+        <v>51</v>
       </c>
       <c r="L19" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="M19">
         <v>0.1</v>
@@ -2082,7 +2074,7 @@
         <v>19</v>
       </c>
       <c r="E20" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G20" t="s">
         <v>36</v>
@@ -2091,10 +2083,10 @@
         <v>26</v>
       </c>
       <c r="K20" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="L20" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="M20">
         <v>0.1</v>
@@ -2135,17 +2127,18 @@
         <f t="shared" si="3"/>
         <v>20</v>
       </c>
-      <c r="E21" t="s">
-        <v>52</v>
+      <c r="E21" t="str">
+        <f t="shared" ref="E21:E22" si="4">TEXT(C21,"00") &amp; " GICS-"&amp;K21&amp;" ("&amp;Q21&amp;IF(P21&lt;&gt;"","+ ","")&amp;P21&amp;")"</f>
+        <v>20 GICS-rsi (beta3m)</v>
       </c>
       <c r="G21" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="H21" t="s">
         <v>26</v>
       </c>
       <c r="K21" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="L21" t="s">
         <v>28</v>
@@ -2190,8 +2183,8 @@
         <v>21</v>
       </c>
       <c r="E22" t="str">
-        <f t="shared" ref="E22:E23" si="4">TEXT(C22,"00") &amp; " GICS-"&amp;K22&amp;" ("&amp;Q22&amp;IF(P22&lt;&gt;"","+ ","")&amp;P22&amp;")"</f>
-        <v>21 GICS-rsi (beta3m)</v>
+        <f t="shared" si="4"/>
+        <v>21 GICS-spr100d (beta3m)</v>
       </c>
       <c r="G22" t="s">
         <v>25</v>
@@ -2200,10 +2193,10 @@
         <v>26</v>
       </c>
       <c r="K22" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="L22" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="M22">
         <v>0.1</v>
@@ -2244,21 +2237,20 @@
         <f t="shared" si="3"/>
         <v>22</v>
       </c>
-      <c r="E23" t="str">
-        <f t="shared" si="4"/>
-        <v>22 GICS-spr100d (beta3m)</v>
+      <c r="E23" t="s">
+        <v>54</v>
       </c>
       <c r="G23" t="s">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="H23" t="s">
         <v>26</v>
       </c>
       <c r="K23" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="L23" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="M23">
         <v>0.1</v>
@@ -2300,7 +2292,7 @@
         <v>23</v>
       </c>
       <c r="E24" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G24" t="s">
         <v>55</v>
@@ -2309,7 +2301,7 @@
         <v>26</v>
       </c>
       <c r="K24" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="L24" t="s">
         <v>28</v>
@@ -2354,7 +2346,7 @@
         <v>24</v>
       </c>
       <c r="E25" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G25" t="s">
         <v>55</v>
@@ -2363,10 +2355,10 @@
         <v>26</v>
       </c>
       <c r="K25" t="s">
-        <v>34</v>
+        <v>51</v>
       </c>
       <c r="L25" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="M25">
         <v>0.1</v>
@@ -2407,20 +2399,24 @@
         <f t="shared" si="3"/>
         <v>25</v>
       </c>
-      <c r="E26" t="s">
-        <v>57</v>
+      <c r="E26" t="str">
+        <f t="shared" ref="E26:E71" si="5">TEXT(C26,"00") &amp; " GICS-"&amp;K26&amp;" ("&amp;Q26&amp;IF(P26&lt;&gt;"","+ ","")&amp;P26&amp;")"</f>
+        <v>25 GICS-beta6m (beta6m)</v>
+      </c>
+      <c r="F26" t="s">
+        <v>127</v>
       </c>
       <c r="G26" t="s">
-        <v>55</v>
+        <v>25</v>
       </c>
       <c r="H26" t="s">
         <v>26</v>
       </c>
       <c r="K26" t="s">
-        <v>51</v>
+        <v>126</v>
       </c>
       <c r="L26" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="M26">
         <v>0.1</v>
@@ -2432,7 +2428,7 @@
         <v>4</v>
       </c>
       <c r="Q26" t="s">
-        <v>27</v>
+        <v>126</v>
       </c>
       <c r="R26" t="s">
         <v>28</v>
@@ -2462,8 +2458,8 @@
         <v>26</v>
       </c>
       <c r="E27" t="str">
-        <f t="shared" ref="E27:E72" si="5">TEXT(C27,"00") &amp; " GICS-"&amp;K27&amp;" ("&amp;Q27&amp;IF(P27&lt;&gt;"","+ ","")&amp;P27&amp;")"</f>
-        <v>26 GICS-beta6m (beta6m)</v>
+        <f t="shared" si="5"/>
+        <v>26 GICS-beta3m (beta6m)</v>
       </c>
       <c r="F27" t="s">
         <v>127</v>
@@ -2475,7 +2471,7 @@
         <v>26</v>
       </c>
       <c r="K27" t="s">
-        <v>126</v>
+        <v>27</v>
       </c>
       <c r="L27" t="s">
         <v>28</v>
@@ -2521,7 +2517,7 @@
       </c>
       <c r="E28" t="str">
         <f t="shared" si="5"/>
-        <v>27 GICS-beta3m (beta6m)</v>
+        <v>27 GICS-beta6m (beta3m)</v>
       </c>
       <c r="F28" t="s">
         <v>127</v>
@@ -2533,7 +2529,7 @@
         <v>26</v>
       </c>
       <c r="K28" t="s">
-        <v>27</v>
+        <v>126</v>
       </c>
       <c r="L28" t="s">
         <v>28</v>
@@ -2548,7 +2544,7 @@
         <v>4</v>
       </c>
       <c r="Q28" t="s">
-        <v>126</v>
+        <v>27</v>
       </c>
       <c r="R28" t="s">
         <v>28</v>
@@ -2579,10 +2575,10 @@
       </c>
       <c r="E29" t="str">
         <f t="shared" si="5"/>
-        <v>28 GICS-beta6m (beta3m)</v>
+        <v>28 GICS-beta1m (beta1m)</v>
       </c>
       <c r="F29" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="G29" t="s">
         <v>25</v>
@@ -2591,7 +2587,7 @@
         <v>26</v>
       </c>
       <c r="K29" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="L29" t="s">
         <v>28</v>
@@ -2606,7 +2602,7 @@
         <v>4</v>
       </c>
       <c r="Q29" t="s">
-        <v>27</v>
+        <v>128</v>
       </c>
       <c r="R29" t="s">
         <v>28</v>
@@ -2637,7 +2633,7 @@
       </c>
       <c r="E30" t="str">
         <f t="shared" si="5"/>
-        <v>29 GICS-beta1m (beta1m)</v>
+        <v>29 GICS-beta2m (beta2m)</v>
       </c>
       <c r="F30" t="s">
         <v>130</v>
@@ -2649,7 +2645,7 @@
         <v>26</v>
       </c>
       <c r="K30" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="L30" t="s">
         <v>28</v>
@@ -2664,7 +2660,7 @@
         <v>4</v>
       </c>
       <c r="Q30" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="R30" t="s">
         <v>28</v>
@@ -2695,19 +2691,16 @@
       </c>
       <c r="E31" t="str">
         <f t="shared" si="5"/>
-        <v>30 GICS-beta2m (beta2m)</v>
-      </c>
-      <c r="F31" t="s">
-        <v>130</v>
+        <v>30 GICS-beta3m (beta3m+ Longi.rank&lt;1000)</v>
       </c>
       <c r="G31" t="s">
-        <v>25</v>
+        <v>131</v>
       </c>
       <c r="H31" t="s">
         <v>26</v>
       </c>
       <c r="K31" t="s">
-        <v>129</v>
+        <v>27</v>
       </c>
       <c r="L31" t="s">
         <v>28</v>
@@ -2716,13 +2709,16 @@
         <v>0.1</v>
       </c>
       <c r="N31">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="O31">
         <v>4</v>
       </c>
+      <c r="P31" t="s">
+        <v>132</v>
+      </c>
       <c r="Q31" t="s">
-        <v>129</v>
+        <v>27</v>
       </c>
       <c r="R31" t="s">
         <v>28</v>
@@ -2753,7 +2749,10 @@
       </c>
       <c r="E32" t="str">
         <f t="shared" si="5"/>
-        <v>31 GICS-beta3m (beta3m+ Longi.rank&lt;1000)</v>
+        <v>31 GICS-PdivMA20 (beta3m+ Longi.rank&lt;1000)</v>
+      </c>
+      <c r="F32" t="s">
+        <v>133</v>
       </c>
       <c r="G32" t="s">
         <v>131</v>
@@ -2762,7 +2761,7 @@
         <v>26</v>
       </c>
       <c r="K32" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="L32" t="s">
         <v>28</v>
@@ -2811,10 +2810,10 @@
       </c>
       <c r="E33" t="str">
         <f t="shared" si="5"/>
-        <v>32 GICS-PdivMA20 (beta3m+ Longi.rank&lt;1000)</v>
+        <v>32 GICS-rank (beta3m+ Longi.rank&lt;1000)</v>
       </c>
       <c r="F33" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="G33" t="s">
         <v>131</v>
@@ -2823,10 +2822,10 @@
         <v>26</v>
       </c>
       <c r="K33" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L33" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="M33">
         <v>0.1</v>
@@ -2862,7 +2861,7 @@
         <v>0</v>
       </c>
       <c r="X33" t="s">
-        <v>29</v>
+        <v>135</v>
       </c>
     </row>
     <row r="34" spans="3:24" x14ac:dyDescent="0.25">
@@ -2872,10 +2871,7 @@
       </c>
       <c r="E34" t="str">
         <f t="shared" si="5"/>
-        <v>33 GICS-rank (beta3m+ Longi.rank&lt;1000)</v>
-      </c>
-      <c r="F34" t="s">
-        <v>141</v>
+        <v>33 GICS-sh3m (beta3m+ Longi.rank&lt;1000)</v>
       </c>
       <c r="G34" t="s">
         <v>131</v>
@@ -2884,10 +2880,10 @@
         <v>26</v>
       </c>
       <c r="K34" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="L34" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="M34">
         <v>0.1</v>
@@ -2923,7 +2919,7 @@
         <v>0</v>
       </c>
       <c r="X34" t="s">
-        <v>135</v>
+        <v>29</v>
       </c>
     </row>
     <row r="35" spans="3:24" x14ac:dyDescent="0.25">
@@ -2933,7 +2929,7 @@
       </c>
       <c r="E35" t="str">
         <f t="shared" si="5"/>
-        <v>34 GICS-sh3m (beta3m+ Longi.rank&lt;1000)</v>
+        <v>34 GICS-rsi (beta3m+ Longi.rank&lt;1000)</v>
       </c>
       <c r="G35" t="s">
         <v>131</v>
@@ -2942,7 +2938,7 @@
         <v>26</v>
       </c>
       <c r="K35" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="L35" t="s">
         <v>28</v>
@@ -2991,7 +2987,7 @@
       </c>
       <c r="E36" t="str">
         <f t="shared" si="5"/>
-        <v>35 GICS-rsi (beta3m+ Longi.rank&lt;1000)</v>
+        <v>35 GICS-spr100d (beta3m+ Longi.rank&lt;1000)</v>
       </c>
       <c r="G36" t="s">
         <v>131</v>
@@ -3000,10 +2996,10 @@
         <v>26</v>
       </c>
       <c r="K36" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="L36" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="M36">
         <v>0.1</v>
@@ -3049,7 +3045,7 @@
       </c>
       <c r="E37" t="str">
         <f t="shared" si="5"/>
-        <v>36 GICS-spr100d (beta3m+ Longi.rank&lt;1000)</v>
+        <v>36 GICS-rank (beta3m)</v>
       </c>
       <c r="G37" t="s">
         <v>131</v>
@@ -3058,7 +3054,7 @@
         <v>26</v>
       </c>
       <c r="K37" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="L37" t="s">
         <v>33</v>
@@ -3072,9 +3068,6 @@
       <c r="O37">
         <v>4</v>
       </c>
-      <c r="P37" t="s">
-        <v>132</v>
-      </c>
       <c r="Q37" t="s">
         <v>27</v>
       </c>
@@ -3097,7 +3090,7 @@
         <v>0</v>
       </c>
       <c r="X37" t="s">
-        <v>29</v>
+        <v>135</v>
       </c>
     </row>
     <row r="38" spans="3:24" x14ac:dyDescent="0.25">
@@ -3107,7 +3100,10 @@
       </c>
       <c r="E38" t="str">
         <f t="shared" si="5"/>
-        <v>37 GICS-rank (beta3m)</v>
+        <v>37 GICS-rank (beta3m+ Longi.per1d&gt;0)</v>
+      </c>
+      <c r="F38" t="s">
+        <v>141</v>
       </c>
       <c r="G38" t="s">
         <v>131</v>
@@ -3129,6 +3125,9 @@
       </c>
       <c r="O38">
         <v>4</v>
+      </c>
+      <c r="P38" t="s">
+        <v>136</v>
       </c>
       <c r="Q38" t="s">
         <v>27</v>
@@ -3162,10 +3161,7 @@
       </c>
       <c r="E39" t="str">
         <f t="shared" si="5"/>
-        <v>38 GICS-rank (beta3m+ Longi.per1d&gt;0)</v>
-      </c>
-      <c r="F39" t="s">
-        <v>141</v>
+        <v>38 GICS-rank (beta3m+ Longi.regr20d&gt;0)</v>
       </c>
       <c r="G39" t="s">
         <v>131</v>
@@ -3189,7 +3185,7 @@
         <v>4</v>
       </c>
       <c r="P39" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="Q39" t="s">
         <v>27</v>
@@ -3223,7 +3219,7 @@
       </c>
       <c r="E40" t="str">
         <f t="shared" si="5"/>
-        <v>39 GICS-rank (beta3m+ Longi.regr20d&gt;0)</v>
+        <v>39 GICS-rank (beta3m+ Longi.regr50d&gt;0)</v>
       </c>
       <c r="G40" t="s">
         <v>131</v>
@@ -3247,7 +3243,7 @@
         <v>4</v>
       </c>
       <c r="P40" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="Q40" t="s">
         <v>27</v>
@@ -3281,7 +3277,10 @@
       </c>
       <c r="E41" t="str">
         <f t="shared" si="5"/>
-        <v>40 GICS-rank (beta3m+ Longi.regr50d&gt;0)</v>
+        <v>40 GICS-rank (beta3m+ Longi.median_10d&lt;1100)</v>
+      </c>
+      <c r="F41" t="s">
+        <v>141</v>
       </c>
       <c r="G41" t="s">
         <v>131</v>
@@ -3305,7 +3304,7 @@
         <v>4</v>
       </c>
       <c r="P41" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="Q41" t="s">
         <v>27</v>
@@ -3339,7 +3338,7 @@
       </c>
       <c r="E42" t="str">
         <f t="shared" si="5"/>
-        <v>41 GICS-rank (beta3m+ Longi.median_10d&lt;1100)</v>
+        <v>41 GICS-rank (beta3m+ Longi.median_10d&lt;1000)</v>
       </c>
       <c r="F42" t="s">
         <v>141</v>
@@ -3366,7 +3365,7 @@
         <v>4</v>
       </c>
       <c r="P42" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="Q42" t="s">
         <v>27</v>
@@ -3400,10 +3399,7 @@
       </c>
       <c r="E43" t="str">
         <f t="shared" si="5"/>
-        <v>42 GICS-rank (beta3m+ Longi.median_10d&lt;1000)</v>
-      </c>
-      <c r="F43" t="s">
-        <v>141</v>
+        <v>42 GICS-PdivMA20 (beta3m)</v>
       </c>
       <c r="G43" t="s">
         <v>131</v>
@@ -3412,10 +3408,10 @@
         <v>26</v>
       </c>
       <c r="K43" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L43" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="M43">
         <v>0.1</v>
@@ -3426,9 +3422,6 @@
       <c r="O43">
         <v>4</v>
       </c>
-      <c r="P43" t="s">
-        <v>140</v>
-      </c>
       <c r="Q43" t="s">
         <v>27</v>
       </c>
@@ -3451,120 +3444,126 @@
         <v>0</v>
       </c>
       <c r="X43" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="44" spans="3:24" x14ac:dyDescent="0.25">
-      <c r="C44">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="44" spans="3:24" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="C44" s="11">
         <f t="shared" si="3"/>
         <v>43</v>
       </c>
-      <c r="E44" t="str">
+      <c r="E44" s="11" t="str">
         <f t="shared" si="5"/>
-        <v>43 GICS-PdivMA20 (beta3m)</v>
-      </c>
-      <c r="G44" t="s">
+        <v>43 GICS-rank (beta3m)</v>
+      </c>
+      <c r="F44" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="G44" s="11" t="s">
         <v>131</v>
       </c>
-      <c r="H44" t="s">
-        <v>26</v>
-      </c>
-      <c r="K44" t="s">
-        <v>31</v>
-      </c>
-      <c r="L44" t="s">
-        <v>28</v>
-      </c>
-      <c r="M44">
-        <v>0.1</v>
-      </c>
-      <c r="N44">
+      <c r="H44" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="K44" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="L44" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="M44" s="11">
+        <v>0.1</v>
+      </c>
+      <c r="N44" s="11">
         <v>5</v>
       </c>
-      <c r="O44">
-        <v>4</v>
-      </c>
-      <c r="Q44" t="s">
-        <v>27</v>
-      </c>
-      <c r="R44" t="s">
-        <v>28</v>
-      </c>
-      <c r="S44">
-        <v>1</v>
-      </c>
-      <c r="T44">
-        <v>3</v>
-      </c>
-      <c r="U44">
-        <v>0</v>
-      </c>
-      <c r="V44">
-        <v>20</v>
-      </c>
-      <c r="W44">
-        <v>0</v>
-      </c>
-      <c r="X44" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="45" spans="3:24" s="11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="C45" s="11">
+      <c r="O44" s="11">
+        <v>4</v>
+      </c>
+      <c r="Q44" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="R44" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="S44" s="11">
+        <v>1</v>
+      </c>
+      <c r="T44" s="11">
+        <v>3</v>
+      </c>
+      <c r="U44" s="11">
+        <v>0</v>
+      </c>
+      <c r="V44" s="11">
+        <v>20</v>
+      </c>
+      <c r="W44" s="11">
+        <v>0</v>
+      </c>
+      <c r="X44" s="11" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="45" spans="3:24" x14ac:dyDescent="0.25">
+      <c r="C45">
         <f t="shared" si="3"/>
         <v>44</v>
       </c>
-      <c r="E45" s="11" t="str">
+      <c r="E45" t="str">
         <f t="shared" si="5"/>
-        <v>44 GICS-rank (beta3m)</v>
-      </c>
-      <c r="F45" s="11" t="s">
-        <v>145</v>
-      </c>
-      <c r="G45" s="11" t="s">
+        <v>44 GICS-rank (PdivMA20+ Longi.rank&lt;1000)</v>
+      </c>
+      <c r="F45" t="s">
+        <v>130</v>
+      </c>
+      <c r="G45" t="s">
         <v>131</v>
       </c>
-      <c r="H45" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="K45" s="11" t="s">
+      <c r="H45" t="s">
+        <v>26</v>
+      </c>
+      <c r="K45" t="s">
         <v>32</v>
       </c>
-      <c r="L45" s="11" t="s">
+      <c r="L45" t="s">
         <v>33</v>
       </c>
-      <c r="M45" s="11">
-        <v>0.1</v>
-      </c>
-      <c r="N45" s="11">
+      <c r="M45">
+        <v>0.1</v>
+      </c>
+      <c r="N45">
         <v>5</v>
       </c>
-      <c r="O45" s="11">
-        <v>4</v>
-      </c>
-      <c r="Q45" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="R45" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="S45" s="11">
-        <v>1</v>
-      </c>
-      <c r="T45" s="11">
-        <v>3</v>
-      </c>
-      <c r="U45" s="11">
-        <v>0</v>
-      </c>
-      <c r="V45" s="11">
-        <v>20</v>
-      </c>
-      <c r="W45" s="11">
-        <v>0</v>
-      </c>
-      <c r="X45" s="11" t="s">
-        <v>135</v>
+      <c r="O45">
+        <v>4</v>
+      </c>
+      <c r="P45" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q45" t="s">
+        <v>31</v>
+      </c>
+      <c r="R45" t="s">
+        <v>28</v>
+      </c>
+      <c r="S45">
+        <v>1</v>
+      </c>
+      <c r="T45">
+        <v>3</v>
+      </c>
+      <c r="U45">
+        <v>0</v>
+      </c>
+      <c r="V45">
+        <v>20</v>
+      </c>
+      <c r="W45">
+        <v>0</v>
+      </c>
+      <c r="X45" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="46" spans="3:24" x14ac:dyDescent="0.25">
@@ -3574,7 +3573,7 @@
       </c>
       <c r="E46" t="str">
         <f t="shared" si="5"/>
-        <v>45 GICS-rank (PdivMA20+ Longi.rank&lt;1000)</v>
+        <v>45 GICS-rank (PdivMA20)</v>
       </c>
       <c r="F46" t="s">
         <v>130</v>
@@ -3599,9 +3598,6 @@
       </c>
       <c r="O46">
         <v>4</v>
-      </c>
-      <c r="P46" t="s">
-        <v>132</v>
       </c>
       <c r="Q46" t="s">
         <v>31</v>
@@ -3635,7 +3631,7 @@
       </c>
       <c r="E47" t="str">
         <f t="shared" si="5"/>
-        <v>46 GICS-rank (PdivMA20)</v>
+        <v>46 GICS-rank (beta3m+ Longi.rank&lt;1000)</v>
       </c>
       <c r="F47" t="s">
         <v>130</v>
@@ -3653,7 +3649,7 @@
         <v>33</v>
       </c>
       <c r="M47">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="N47">
         <v>5</v>
@@ -3661,8 +3657,11 @@
       <c r="O47">
         <v>4</v>
       </c>
+      <c r="P47" t="s">
+        <v>132</v>
+      </c>
       <c r="Q47" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="R47" t="s">
         <v>28</v>
@@ -3693,7 +3692,7 @@
       </c>
       <c r="E48" t="str">
         <f t="shared" si="5"/>
-        <v>47 GICS-rank (beta3m+ Longi.rank&lt;1000)</v>
+        <v>47 GICS-rank (beta3m)</v>
       </c>
       <c r="F48" t="s">
         <v>130</v>
@@ -3718,9 +3717,6 @@
       </c>
       <c r="O48">
         <v>4</v>
-      </c>
-      <c r="P48" t="s">
-        <v>132</v>
       </c>
       <c r="Q48" t="s">
         <v>27</v>
@@ -3754,7 +3750,7 @@
       </c>
       <c r="E49" t="str">
         <f t="shared" si="5"/>
-        <v>48 GICS-rank (beta3m)</v>
+        <v>48 GICS-rank (PdivMA20+ Longi.rank&lt;1000)</v>
       </c>
       <c r="F49" t="s">
         <v>130</v>
@@ -3772,16 +3768,19 @@
         <v>33</v>
       </c>
       <c r="M49">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="N49">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O49">
         <v>4</v>
       </c>
+      <c r="P49" t="s">
+        <v>132</v>
+      </c>
       <c r="Q49" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="R49" t="s">
         <v>28</v>
@@ -3812,7 +3811,7 @@
       </c>
       <c r="E50" t="str">
         <f t="shared" si="5"/>
-        <v>49 GICS-rank (PdivMA20+ Longi.rank&lt;1000)</v>
+        <v>49 GICS-rank (PdivMA20)</v>
       </c>
       <c r="F50" t="s">
         <v>130</v>
@@ -3837,9 +3836,6 @@
       </c>
       <c r="O50">
         <v>4</v>
-      </c>
-      <c r="P50" t="s">
-        <v>132</v>
       </c>
       <c r="Q50" t="s">
         <v>31</v>
@@ -3873,7 +3869,7 @@
       </c>
       <c r="E51" t="str">
         <f t="shared" si="5"/>
-        <v>50 GICS-rank (PdivMA20)</v>
+        <v>50 GICS-rank (beta3m+ Longi.rank&lt;1000)</v>
       </c>
       <c r="F51" t="s">
         <v>130</v>
@@ -3899,8 +3895,11 @@
       <c r="O51">
         <v>4</v>
       </c>
+      <c r="P51" t="s">
+        <v>132</v>
+      </c>
       <c r="Q51" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="R51" t="s">
         <v>28</v>
@@ -3931,7 +3930,7 @@
       </c>
       <c r="E52" t="str">
         <f t="shared" si="5"/>
-        <v>51 GICS-rank (beta3m+ Longi.rank&lt;1000)</v>
+        <v>51 GICS-rank (beta3m)</v>
       </c>
       <c r="F52" t="s">
         <v>130</v>
@@ -3956,9 +3955,6 @@
       </c>
       <c r="O52">
         <v>4</v>
-      </c>
-      <c r="P52" t="s">
-        <v>132</v>
       </c>
       <c r="Q52" t="s">
         <v>27</v>
@@ -3992,13 +3988,13 @@
       </c>
       <c r="E53" t="str">
         <f t="shared" si="5"/>
-        <v>52 GICS-rank (beta3m)</v>
+        <v>52 GICS-rank (rsi)</v>
       </c>
       <c r="F53" t="s">
         <v>130</v>
       </c>
       <c r="G53" t="s">
-        <v>131</v>
+        <v>25</v>
       </c>
       <c r="H53" t="s">
         <v>26</v>
@@ -4013,13 +4009,13 @@
         <v>0.1</v>
       </c>
       <c r="N53">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="O53">
         <v>4</v>
       </c>
       <c r="Q53" t="s">
-        <v>27</v>
+        <v>48</v>
       </c>
       <c r="R53" t="s">
         <v>28</v>
@@ -4040,7 +4036,7 @@
         <v>0</v>
       </c>
       <c r="X53" t="s">
-        <v>29</v>
+        <v>135</v>
       </c>
     </row>
     <row r="54" spans="3:24" x14ac:dyDescent="0.25">
@@ -4050,10 +4046,10 @@
       </c>
       <c r="E54" t="str">
         <f t="shared" si="5"/>
-        <v>53 GICS-rank (rsi)</v>
+        <v>53 GICS-rank (rank)</v>
       </c>
       <c r="F54" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="G54" t="s">
         <v>25</v>
@@ -4077,10 +4073,10 @@
         <v>4</v>
       </c>
       <c r="Q54" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="R54" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="S54">
         <v>1</v>
@@ -4108,10 +4104,10 @@
       </c>
       <c r="E55" t="str">
         <f t="shared" si="5"/>
-        <v>54 GICS-rank (rank)</v>
+        <v>54 GICS-rank (rsi)</v>
       </c>
       <c r="F55" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="G55" t="s">
         <v>25</v>
@@ -4135,13 +4131,13 @@
         <v>4</v>
       </c>
       <c r="Q55" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="R55" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="S55">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="T55">
         <v>3</v>
@@ -4159,116 +4155,119 @@
         <v>135</v>
       </c>
     </row>
-    <row r="56" spans="3:24" x14ac:dyDescent="0.25">
-      <c r="C56">
+    <row r="56" spans="3:24" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="C56" s="9">
         <f t="shared" si="3"/>
         <v>55</v>
       </c>
-      <c r="E56" t="str">
+      <c r="E56" s="9" t="str">
         <f t="shared" si="5"/>
-        <v>55 GICS-rank (rsi)</v>
-      </c>
-      <c r="F56" t="s">
-        <v>130</v>
-      </c>
-      <c r="G56" t="s">
+        <v>55 GICS-rank (rank)</v>
+      </c>
+      <c r="F56" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="G56" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="H56" t="s">
-        <v>26</v>
-      </c>
-      <c r="K56" t="s">
+      <c r="H56" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="K56" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="L56" t="s">
+      <c r="L56" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="M56">
-        <v>0.1</v>
-      </c>
-      <c r="N56">
+      <c r="M56" s="9">
+        <v>0.1</v>
+      </c>
+      <c r="N56" s="9">
         <v>10</v>
       </c>
-      <c r="O56">
-        <v>4</v>
-      </c>
-      <c r="Q56" t="s">
-        <v>48</v>
-      </c>
-      <c r="R56" t="s">
-        <v>28</v>
-      </c>
-      <c r="S56">
+      <c r="O56" s="9">
+        <v>4</v>
+      </c>
+      <c r="Q56" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="R56" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="S56" s="9">
         <v>-1</v>
       </c>
-      <c r="T56">
-        <v>3</v>
-      </c>
-      <c r="U56">
-        <v>0</v>
-      </c>
-      <c r="V56">
-        <v>20</v>
-      </c>
-      <c r="W56">
+      <c r="T56" s="9">
+        <v>3</v>
+      </c>
+      <c r="U56" s="9">
+        <v>0</v>
+      </c>
+      <c r="V56" s="9">
+        <v>20</v>
+      </c>
+      <c r="W56" s="9">
         <v>0</v>
       </c>
       <c r="X56" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="57" spans="3:24" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="C57" s="9">
+    <row r="57" spans="3:24" x14ac:dyDescent="0.25">
+      <c r="C57">
         <f t="shared" si="3"/>
         <v>56</v>
       </c>
-      <c r="E57" s="9" t="str">
+      <c r="E57" t="str">
         <f t="shared" si="5"/>
-        <v>56 GICS-rank (rank)</v>
-      </c>
-      <c r="F57" s="9" t="s">
-        <v>134</v>
-      </c>
-      <c r="G57" s="9" t="s">
+        <v>56 GICS-beta3m (beta3m+ Longi.beta3m&gt;2.5)</v>
+      </c>
+      <c r="F57" t="s">
+        <v>146</v>
+      </c>
+      <c r="G57" t="s">
         <v>25</v>
       </c>
-      <c r="H57" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="K57" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="L57" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="M57" s="9">
-        <v>0.1</v>
-      </c>
-      <c r="N57" s="9">
+      <c r="H57" t="s">
+        <v>26</v>
+      </c>
+      <c r="K57" t="s">
+        <v>27</v>
+      </c>
+      <c r="L57" t="s">
+        <v>28</v>
+      </c>
+      <c r="M57">
+        <v>0.1</v>
+      </c>
+      <c r="N57">
         <v>10</v>
       </c>
-      <c r="O57" s="9">
-        <v>4</v>
-      </c>
-      <c r="Q57" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="R57" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="S57" s="9">
-        <v>-1</v>
-      </c>
-      <c r="T57" s="9">
-        <v>3</v>
-      </c>
-      <c r="U57" s="9">
-        <v>0</v>
-      </c>
-      <c r="V57" s="9">
-        <v>20</v>
-      </c>
-      <c r="W57" s="9">
+      <c r="O57">
+        <v>4</v>
+      </c>
+      <c r="P57" t="s">
+        <v>143</v>
+      </c>
+      <c r="Q57" t="s">
+        <v>27</v>
+      </c>
+      <c r="R57" t="s">
+        <v>28</v>
+      </c>
+      <c r="S57">
+        <v>1</v>
+      </c>
+      <c r="T57">
+        <v>1</v>
+      </c>
+      <c r="U57">
+        <v>0</v>
+      </c>
+      <c r="V57">
+        <v>20</v>
+      </c>
+      <c r="W57">
         <v>0</v>
       </c>
       <c r="X57" t="s">
@@ -4321,7 +4320,7 @@
         <v>1</v>
       </c>
       <c r="T58">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="U58">
         <v>0</v>
@@ -4336,125 +4335,125 @@
         <v>135</v>
       </c>
     </row>
-    <row r="59" spans="3:24" x14ac:dyDescent="0.25">
-      <c r="C59">
+    <row r="59" spans="3:24" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="C59" s="9">
         <f t="shared" si="3"/>
         <v>58</v>
       </c>
-      <c r="E59" t="str">
+      <c r="E59" s="9" t="str">
         <f t="shared" si="5"/>
         <v>58 GICS-beta3m (beta3m+ Longi.beta3m&gt;2.5)</v>
       </c>
-      <c r="F59" t="s">
+      <c r="F59" s="9" t="s">
         <v>146</v>
       </c>
-      <c r="G59" t="s">
+      <c r="G59" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="H59" t="s">
-        <v>26</v>
-      </c>
-      <c r="K59" t="s">
-        <v>27</v>
-      </c>
-      <c r="L59" t="s">
-        <v>28</v>
-      </c>
-      <c r="M59">
-        <v>0.1</v>
-      </c>
-      <c r="N59">
+      <c r="H59" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="K59" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="L59" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="M59" s="9">
+        <v>0.1</v>
+      </c>
+      <c r="N59" s="9">
         <v>10</v>
       </c>
-      <c r="O59">
-        <v>4</v>
-      </c>
-      <c r="P59" t="s">
+      <c r="O59" s="9">
+        <v>4</v>
+      </c>
+      <c r="P59" s="9" t="s">
         <v>143</v>
       </c>
-      <c r="Q59" t="s">
-        <v>27</v>
-      </c>
-      <c r="R59" t="s">
-        <v>28</v>
-      </c>
-      <c r="S59">
-        <v>1</v>
-      </c>
-      <c r="T59">
-        <v>5</v>
-      </c>
-      <c r="U59">
-        <v>0</v>
-      </c>
-      <c r="V59">
-        <v>20</v>
-      </c>
-      <c r="W59">
-        <v>0</v>
-      </c>
-      <c r="X59" t="s">
+      <c r="Q59" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="R59" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="S59" s="9">
+        <v>1</v>
+      </c>
+      <c r="T59" s="9">
+        <v>10</v>
+      </c>
+      <c r="U59" s="9">
+        <v>0</v>
+      </c>
+      <c r="V59" s="9">
+        <v>20</v>
+      </c>
+      <c r="W59" s="9">
+        <v>0</v>
+      </c>
+      <c r="X59" s="9" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="60" spans="3:24" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="C60" s="9">
+    <row r="60" spans="3:24" x14ac:dyDescent="0.25">
+      <c r="C60">
         <f t="shared" si="3"/>
         <v>59</v>
       </c>
-      <c r="E60" s="9" t="str">
+      <c r="E60" t="str">
         <f t="shared" si="5"/>
         <v>59 GICS-beta3m (beta3m+ Longi.beta3m&gt;2.5)</v>
       </c>
-      <c r="F60" s="9" t="s">
-        <v>146</v>
-      </c>
-      <c r="G60" s="9" t="s">
+      <c r="F60" t="s">
+        <v>147</v>
+      </c>
+      <c r="G60" t="s">
         <v>25</v>
       </c>
-      <c r="H60" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="K60" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="L60" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="M60" s="9">
-        <v>0.1</v>
-      </c>
-      <c r="N60" s="9">
+      <c r="H60" t="s">
+        <v>26</v>
+      </c>
+      <c r="K60" t="s">
+        <v>27</v>
+      </c>
+      <c r="L60" t="s">
+        <v>28</v>
+      </c>
+      <c r="M60">
+        <v>0.1</v>
+      </c>
+      <c r="N60">
         <v>10</v>
       </c>
-      <c r="O60" s="9">
-        <v>4</v>
-      </c>
-      <c r="P60" s="9" t="s">
+      <c r="O60">
+        <v>6</v>
+      </c>
+      <c r="P60" t="s">
         <v>143</v>
       </c>
-      <c r="Q60" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="R60" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="S60" s="9">
-        <v>1</v>
-      </c>
-      <c r="T60" s="9">
-        <v>10</v>
-      </c>
-      <c r="U60" s="9">
-        <v>0</v>
-      </c>
-      <c r="V60" s="9">
-        <v>20</v>
-      </c>
-      <c r="W60" s="9">
-        <v>0</v>
-      </c>
-      <c r="X60" s="9" t="s">
+      <c r="Q60" t="s">
+        <v>27</v>
+      </c>
+      <c r="R60" t="s">
+        <v>28</v>
+      </c>
+      <c r="S60">
+        <v>1</v>
+      </c>
+      <c r="T60">
+        <v>3</v>
+      </c>
+      <c r="U60">
+        <v>0</v>
+      </c>
+      <c r="V60">
+        <v>20</v>
+      </c>
+      <c r="W60">
+        <v>0</v>
+      </c>
+      <c r="X60" t="s">
         <v>135</v>
       </c>
     </row>
@@ -4489,7 +4488,7 @@
         <v>10</v>
       </c>
       <c r="O61">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="P61" t="s">
         <v>143</v>
@@ -4519,126 +4518,126 @@
         <v>135</v>
       </c>
     </row>
-    <row r="62" spans="3:24" x14ac:dyDescent="0.25">
-      <c r="C62">
+    <row r="62" spans="3:24" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="C62" s="9">
         <f t="shared" si="3"/>
         <v>61</v>
       </c>
-      <c r="E62" t="str">
+      <c r="E62" s="9" t="str">
         <f t="shared" si="5"/>
         <v>61 GICS-beta3m (beta3m+ Longi.beta3m&gt;2.5)</v>
       </c>
-      <c r="F62" t="s">
+      <c r="F62" s="9" t="s">
         <v>147</v>
       </c>
-      <c r="G62" t="s">
+      <c r="G62" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="H62" t="s">
-        <v>26</v>
-      </c>
-      <c r="K62" t="s">
-        <v>27</v>
-      </c>
-      <c r="L62" t="s">
-        <v>28</v>
-      </c>
-      <c r="M62">
-        <v>0.1</v>
-      </c>
-      <c r="N62">
+      <c r="H62" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="K62" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="L62" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="M62" s="9">
+        <v>0.1</v>
+      </c>
+      <c r="N62" s="9">
         <v>10</v>
       </c>
-      <c r="O62">
-        <v>8</v>
-      </c>
-      <c r="P62" t="s">
+      <c r="O62" s="9">
+        <v>10</v>
+      </c>
+      <c r="P62" s="9" t="s">
         <v>143</v>
       </c>
-      <c r="Q62" t="s">
-        <v>27</v>
-      </c>
-      <c r="R62" t="s">
-        <v>28</v>
-      </c>
-      <c r="S62">
-        <v>1</v>
-      </c>
-      <c r="T62">
-        <v>3</v>
-      </c>
-      <c r="U62">
-        <v>0</v>
-      </c>
-      <c r="V62">
-        <v>20</v>
-      </c>
-      <c r="W62">
-        <v>0</v>
-      </c>
-      <c r="X62" t="s">
+      <c r="Q62" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="R62" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="S62" s="9">
+        <v>1</v>
+      </c>
+      <c r="T62" s="9">
+        <v>3</v>
+      </c>
+      <c r="U62" s="9">
+        <v>0</v>
+      </c>
+      <c r="V62" s="9">
+        <v>20</v>
+      </c>
+      <c r="W62" s="9">
+        <v>0</v>
+      </c>
+      <c r="X62" s="9" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="63" spans="3:24" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="C63" s="9">
+    <row r="63" spans="3:24" x14ac:dyDescent="0.25">
+      <c r="C63">
         <f t="shared" si="3"/>
         <v>62</v>
       </c>
-      <c r="E63" s="9" t="str">
+      <c r="E63" t="str">
         <f t="shared" si="5"/>
-        <v>62 GICS-beta3m (beta3m+ Longi.beta3m&gt;2.5)</v>
-      </c>
-      <c r="F63" s="9" t="s">
-        <v>147</v>
-      </c>
-      <c r="G63" s="9" t="s">
+        <v>62 GICS-beta3m (beta3m+ Longi.rank&lt;1000)</v>
+      </c>
+      <c r="F63" t="s">
+        <v>150</v>
+      </c>
+      <c r="G63" t="s">
         <v>25</v>
       </c>
-      <c r="H63" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="K63" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="L63" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="M63" s="9">
-        <v>0.1</v>
-      </c>
-      <c r="N63" s="9">
+      <c r="H63" t="s">
+        <v>26</v>
+      </c>
+      <c r="K63" t="s">
+        <v>27</v>
+      </c>
+      <c r="L63" t="s">
+        <v>28</v>
+      </c>
+      <c r="M63">
+        <v>0.15</v>
+      </c>
+      <c r="N63">
         <v>10</v>
       </c>
-      <c r="O63" s="9">
-        <v>10</v>
-      </c>
-      <c r="P63" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="Q63" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="R63" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="S63" s="9">
-        <v>1</v>
-      </c>
-      <c r="T63" s="9">
-        <v>3</v>
-      </c>
-      <c r="U63" s="9">
-        <v>0</v>
-      </c>
-      <c r="V63" s="9">
-        <v>20</v>
-      </c>
-      <c r="W63" s="9">
-        <v>0</v>
-      </c>
-      <c r="X63" s="9" t="s">
-        <v>135</v>
+      <c r="O63">
+        <v>4</v>
+      </c>
+      <c r="P63" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q63" t="s">
+        <v>27</v>
+      </c>
+      <c r="R63" t="s">
+        <v>28</v>
+      </c>
+      <c r="S63">
+        <v>1</v>
+      </c>
+      <c r="T63">
+        <v>3</v>
+      </c>
+      <c r="U63">
+        <v>0</v>
+      </c>
+      <c r="V63">
+        <v>20</v>
+      </c>
+      <c r="W63">
+        <v>0</v>
+      </c>
+      <c r="X63" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="64" spans="3:24" x14ac:dyDescent="0.25">
@@ -4648,7 +4647,7 @@
       </c>
       <c r="E64" t="str">
         <f t="shared" si="5"/>
-        <v>63 GICS-beta3m (beta3m+ Longi.rank&lt;1000)</v>
+        <v>63 GICS-beta3m (beta3m+ Longi.beta3m&gt;2.5)</v>
       </c>
       <c r="F64" t="s">
         <v>150</v>
@@ -4675,7 +4674,7 @@
         <v>4</v>
       </c>
       <c r="P64" t="s">
-        <v>132</v>
+        <v>143</v>
       </c>
       <c r="Q64" t="s">
         <v>27</v>
@@ -4709,7 +4708,7 @@
       </c>
       <c r="E65" t="str">
         <f t="shared" si="5"/>
-        <v>64 GICS-beta3m (beta3m+ Longi.beta3m&gt;2.5)</v>
+        <v>64 GICS-beta3m (beta3m+ Longi.rank&lt;1000)</v>
       </c>
       <c r="F65" t="s">
         <v>150</v>
@@ -4736,7 +4735,7 @@
         <v>4</v>
       </c>
       <c r="P65" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="Q65" t="s">
         <v>27</v>
@@ -4751,7 +4750,7 @@
         <v>3</v>
       </c>
       <c r="U65">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="V65">
         <v>20</v>
@@ -4770,7 +4769,7 @@
       </c>
       <c r="E66" t="str">
         <f t="shared" si="5"/>
-        <v>65 GICS-beta3m (beta3m+ Longi.rank&lt;1000)</v>
+        <v>65 GICS-beta3m (beta3m+ Longi.beta3m&gt;2.5)</v>
       </c>
       <c r="F66" t="s">
         <v>150</v>
@@ -4797,7 +4796,7 @@
         <v>4</v>
       </c>
       <c r="P66" t="s">
-        <v>132</v>
+        <v>143</v>
       </c>
       <c r="Q66" t="s">
         <v>27</v>
@@ -4831,7 +4830,7 @@
       </c>
       <c r="E67" t="str">
         <f t="shared" si="5"/>
-        <v>66 GICS-beta3m (beta3m+ Longi.beta3m&gt;2.5)</v>
+        <v>66 GICS-beta3m (beta3m)</v>
       </c>
       <c r="F67" t="s">
         <v>150</v>
@@ -4849,7 +4848,7 @@
         <v>28</v>
       </c>
       <c r="M67">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="N67">
         <v>10</v>
@@ -4857,9 +4856,6 @@
       <c r="O67">
         <v>4</v>
       </c>
-      <c r="P67" t="s">
-        <v>143</v>
-      </c>
       <c r="Q67" t="s">
         <v>27</v>
       </c>
@@ -4873,7 +4869,7 @@
         <v>3</v>
       </c>
       <c r="U67">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="V67">
         <v>20</v>
@@ -4892,7 +4888,7 @@
       </c>
       <c r="E68" t="str">
         <f t="shared" si="5"/>
-        <v>67 GICS-beta3m (beta3m)</v>
+        <v>67 GICS-beta3m (beta3m+ Longi.rank&lt;1000 .and. Longi.beta3m&gt;2.5)</v>
       </c>
       <c r="F68" t="s">
         <v>150</v>
@@ -4918,6 +4914,9 @@
       <c r="O68">
         <v>4</v>
       </c>
+      <c r="P68" t="s">
+        <v>149</v>
+      </c>
       <c r="Q68" t="s">
         <v>27</v>
       </c>
@@ -4943,126 +4942,129 @@
         <v>148</v>
       </c>
     </row>
-    <row r="69" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="C69">
+    <row r="69" spans="1:24" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="C69" s="9">
         <f t="shared" si="3"/>
         <v>68</v>
       </c>
-      <c r="E69" t="str">
+      <c r="E69" s="9" t="str">
         <f t="shared" si="5"/>
         <v>68 GICS-beta3m (beta3m+ Longi.rank&lt;1000 .and. Longi.beta3m&gt;2.5)</v>
       </c>
-      <c r="F69" t="s">
+      <c r="F69" s="9" t="s">
         <v>150</v>
       </c>
-      <c r="G69" t="s">
+      <c r="G69" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="H69" t="s">
-        <v>26</v>
-      </c>
-      <c r="K69" t="s">
-        <v>27</v>
-      </c>
-      <c r="L69" t="s">
-        <v>28</v>
-      </c>
-      <c r="M69">
-        <v>0.1</v>
-      </c>
-      <c r="N69">
+      <c r="H69" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="K69" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="L69" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="M69" s="9">
+        <v>0.1</v>
+      </c>
+      <c r="N69" s="9">
         <v>10</v>
       </c>
-      <c r="O69">
-        <v>4</v>
-      </c>
-      <c r="P69" t="s">
+      <c r="O69" s="9">
+        <v>5</v>
+      </c>
+      <c r="P69" s="9" t="s">
         <v>149</v>
       </c>
-      <c r="Q69" t="s">
-        <v>27</v>
-      </c>
-      <c r="R69" t="s">
-        <v>28</v>
-      </c>
-      <c r="S69">
-        <v>1</v>
-      </c>
-      <c r="T69">
-        <v>3</v>
-      </c>
-      <c r="U69">
-        <v>0</v>
-      </c>
-      <c r="V69">
-        <v>20</v>
-      </c>
-      <c r="W69">
-        <v>0</v>
-      </c>
-      <c r="X69" t="s">
+      <c r="Q69" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="R69" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="S69" s="9">
+        <v>1</v>
+      </c>
+      <c r="T69" s="9">
+        <v>3</v>
+      </c>
+      <c r="U69" s="9">
+        <v>0</v>
+      </c>
+      <c r="V69" s="9">
+        <v>20</v>
+      </c>
+      <c r="W69" s="9">
+        <v>0</v>
+      </c>
+      <c r="X69" s="9" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="70" spans="1:24" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="C70" s="9">
-        <f t="shared" si="3"/>
+    <row r="70" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="C70">
+        <f>C69+1</f>
         <v>69</v>
       </c>
-      <c r="E70" s="9" t="str">
+      <c r="D70" t="s">
+        <v>153</v>
+      </c>
+      <c r="E70" t="str">
         <f t="shared" si="5"/>
-        <v>69 GICS-beta3m (beta3m+ Longi.rank&lt;1000 .and. Longi.beta3m&gt;2.5)</v>
-      </c>
-      <c r="F70" s="9" t="s">
-        <v>150</v>
-      </c>
-      <c r="G70" s="9" t="s">
+        <v>69 GICS-beta2m (beta3m+ Longi.beta3m&gt;2.5)</v>
+      </c>
+      <c r="F70" t="s">
+        <v>156</v>
+      </c>
+      <c r="G70" t="s">
         <v>25</v>
       </c>
-      <c r="H70" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="K70" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="L70" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="M70" s="9">
-        <v>0.1</v>
-      </c>
-      <c r="N70" s="9">
+      <c r="H70" t="s">
+        <v>26</v>
+      </c>
+      <c r="K70" t="s">
+        <v>129</v>
+      </c>
+      <c r="L70" t="s">
+        <v>28</v>
+      </c>
+      <c r="M70">
+        <v>0.1</v>
+      </c>
+      <c r="N70">
         <v>10</v>
       </c>
-      <c r="O70" s="9">
-        <v>5</v>
-      </c>
-      <c r="P70" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="Q70" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="R70" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="S70" s="9">
-        <v>1</v>
-      </c>
-      <c r="T70" s="9">
-        <v>3</v>
-      </c>
-      <c r="U70" s="9">
-        <v>0</v>
-      </c>
-      <c r="V70" s="9">
-        <v>20</v>
-      </c>
-      <c r="W70" s="9">
-        <v>0</v>
-      </c>
-      <c r="X70" s="9" t="s">
-        <v>148</v>
+      <c r="O70">
+        <v>4</v>
+      </c>
+      <c r="P70" t="s">
+        <v>143</v>
+      </c>
+      <c r="Q70" t="s">
+        <v>27</v>
+      </c>
+      <c r="R70" t="s">
+        <v>28</v>
+      </c>
+      <c r="S70">
+        <v>1</v>
+      </c>
+      <c r="T70">
+        <v>3</v>
+      </c>
+      <c r="U70">
+        <v>0</v>
+      </c>
+      <c r="V70">
+        <v>20</v>
+      </c>
+      <c r="W70">
+        <v>0</v>
+      </c>
+      <c r="X70" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="71" spans="1:24" x14ac:dyDescent="0.25">
@@ -5075,7 +5077,7 @@
       </c>
       <c r="E71" t="str">
         <f t="shared" si="5"/>
-        <v>70 GICS-beta2m (beta3m+ Longi.beta3m&gt;2.5)</v>
+        <v>70 GICS-beta1m (beta3m+ Longi.beta3m&gt;2.5)</v>
       </c>
       <c r="F71" t="s">
         <v>156</v>
@@ -5086,8 +5088,8 @@
       <c r="H71" t="s">
         <v>26</v>
       </c>
-      <c r="K71" s="12" t="s">
-        <v>129</v>
+      <c r="K71" t="s">
+        <v>128</v>
       </c>
       <c r="L71" t="s">
         <v>28</v>
@@ -5101,7 +5103,7 @@
       <c r="O71">
         <v>4</v>
       </c>
-      <c r="P71" s="12" t="s">
+      <c r="P71" t="s">
         <v>143</v>
       </c>
       <c r="Q71" t="s">
@@ -5138,8 +5140,8 @@
         <v>153</v>
       </c>
       <c r="E72" t="str">
-        <f t="shared" si="5"/>
-        <v>71 GICS-beta1m (beta3m+ Longi.beta3m&gt;2.5)</v>
+        <f t="shared" ref="E72:E73" si="6">TEXT(C72,"00") &amp; " GICS-"&amp;K72&amp;" ("&amp;Q72&amp;IF(P72&lt;&gt;"","+ ","")&amp;P72&amp;")"</f>
+        <v>71 GICS-beta2m (beta3m)</v>
       </c>
       <c r="F72" t="s">
         <v>156</v>
@@ -5150,8 +5152,8 @@
       <c r="H72" t="s">
         <v>26</v>
       </c>
-      <c r="K72" s="12" t="s">
-        <v>128</v>
+      <c r="K72" t="s">
+        <v>129</v>
       </c>
       <c r="L72" t="s">
         <v>28</v>
@@ -5164,9 +5166,6 @@
       </c>
       <c r="O72">
         <v>4</v>
-      </c>
-      <c r="P72" s="12" t="s">
-        <v>143</v>
       </c>
       <c r="Q72" t="s">
         <v>27</v>
@@ -5202,8 +5201,8 @@
         <v>153</v>
       </c>
       <c r="E73" t="str">
-        <f t="shared" ref="E73:E74" si="6">TEXT(C73,"00") &amp; " GICS-"&amp;K73&amp;" ("&amp;Q73&amp;IF(P73&lt;&gt;"","+ ","")&amp;P73&amp;")"</f>
-        <v>72 GICS-beta2m (beta3m)</v>
+        <f t="shared" si="6"/>
+        <v>72 GICS-beta1m (beta3m)</v>
       </c>
       <c r="F73" t="s">
         <v>156</v>
@@ -5214,8 +5213,8 @@
       <c r="H73" t="s">
         <v>26</v>
       </c>
-      <c r="K73" s="12" t="s">
-        <v>129</v>
+      <c r="K73" t="s">
+        <v>128</v>
       </c>
       <c r="L73" t="s">
         <v>28</v>
@@ -5229,7 +5228,6 @@
       <c r="O73">
         <v>4</v>
       </c>
-      <c r="P73" s="12"/>
       <c r="Q73" t="s">
         <v>27</v>
       </c>
@@ -5264,8 +5262,8 @@
         <v>153</v>
       </c>
       <c r="E74" t="str">
-        <f t="shared" si="6"/>
-        <v>73 GICS-beta1m (beta3m)</v>
+        <f t="shared" ref="E74" si="7">TEXT(C74,"00") &amp; " GICS-"&amp;K74&amp;" ("&amp;Q74&amp;IF(P74&lt;&gt;"","+ ","")&amp;P74&amp;")"</f>
+        <v>73 GICS-beta2m (beta3m)</v>
       </c>
       <c r="F74" t="s">
         <v>156</v>
@@ -5276,8 +5274,8 @@
       <c r="H74" t="s">
         <v>26</v>
       </c>
-      <c r="K74" s="12" t="s">
-        <v>128</v>
+      <c r="K74" t="s">
+        <v>129</v>
       </c>
       <c r="L74" t="s">
         <v>28</v>
@@ -5289,9 +5287,8 @@
         <v>10</v>
       </c>
       <c r="O74">
-        <v>4</v>
-      </c>
-      <c r="P74" s="12"/>
+        <v>5</v>
+      </c>
       <c r="Q74" t="s">
         <v>27</v>
       </c>
@@ -5319,18 +5316,18 @@
     </row>
     <row r="75" spans="1:24" x14ac:dyDescent="0.25">
       <c r="C75">
-        <f>C74+1</f>
+        <f t="shared" ref="C75:C76" si="8">C74+1</f>
         <v>74</v>
       </c>
       <c r="D75" t="s">
         <v>153</v>
       </c>
       <c r="E75" t="str">
-        <f t="shared" ref="E75" si="7">TEXT(C75,"00") &amp; " GICS-"&amp;K75&amp;" ("&amp;Q75&amp;IF(P75&lt;&gt;"","+ ","")&amp;P75&amp;")"</f>
+        <f t="shared" ref="E75:E76" si="9">TEXT(C75,"00") &amp; " GICS-"&amp;K75&amp;" ("&amp;Q75&amp;IF(P75&lt;&gt;"","+ ","")&amp;P75&amp;")"</f>
         <v>74 GICS-beta2m (beta3m)</v>
       </c>
       <c r="F75" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G75" t="s">
         <v>25</v>
@@ -5350,8 +5347,8 @@
       <c r="N75">
         <v>10</v>
       </c>
-      <c r="O75" s="12">
-        <v>5</v>
+      <c r="O75">
+        <v>4</v>
       </c>
       <c r="Q75" t="s">
         <v>27</v>
@@ -5360,7 +5357,7 @@
         <v>28</v>
       </c>
       <c r="S75">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T75">
         <v>3</v>
@@ -5378,142 +5375,142 @@
         <v>135</v>
       </c>
     </row>
-    <row r="76" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="C76">
-        <f t="shared" ref="C76:C77" si="8">C75+1</f>
+    <row r="76" spans="1:24" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="C76" s="9">
+        <f t="shared" si="8"/>
         <v>75</v>
       </c>
-      <c r="D76" t="s">
+      <c r="D76" s="9" t="s">
         <v>153</v>
       </c>
-      <c r="E76" t="str">
-        <f t="shared" ref="E76:E77" si="9">TEXT(C76,"00") &amp; " GICS-"&amp;K76&amp;" ("&amp;Q76&amp;IF(P76&lt;&gt;"","+ ","")&amp;P76&amp;")"</f>
+      <c r="E76" s="9" t="str">
+        <f t="shared" si="9"/>
         <v>75 GICS-beta2m (beta3m)</v>
       </c>
-      <c r="F76" t="s">
+      <c r="F76" s="9" t="s">
         <v>155</v>
       </c>
-      <c r="G76" t="s">
+      <c r="G76" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="H76" t="s">
-        <v>26</v>
-      </c>
-      <c r="K76" t="s">
+      <c r="H76" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="K76" s="9" t="s">
         <v>129</v>
       </c>
-      <c r="L76" t="s">
-        <v>28</v>
-      </c>
-      <c r="M76">
-        <v>0.1</v>
-      </c>
-      <c r="N76">
+      <c r="L76" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="M76" s="9">
+        <v>0.1</v>
+      </c>
+      <c r="N76" s="9">
         <v>10</v>
       </c>
-      <c r="O76">
-        <v>4</v>
-      </c>
-      <c r="Q76" t="s">
-        <v>27</v>
-      </c>
-      <c r="R76" t="s">
-        <v>28</v>
-      </c>
-      <c r="S76" s="12">
-        <v>3</v>
-      </c>
-      <c r="T76">
-        <v>3</v>
-      </c>
-      <c r="U76">
-        <v>0</v>
-      </c>
-      <c r="V76">
-        <v>20</v>
-      </c>
-      <c r="W76">
-        <v>0</v>
-      </c>
-      <c r="X76" t="s">
+      <c r="O76" s="9">
+        <v>4</v>
+      </c>
+      <c r="Q76" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="R76" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="S76" s="9" t="s">
+        <v>154</v>
+      </c>
+      <c r="T76" s="9">
+        <v>3</v>
+      </c>
+      <c r="U76" s="9">
+        <v>0</v>
+      </c>
+      <c r="V76" s="9">
+        <v>20</v>
+      </c>
+      <c r="W76" s="9">
+        <v>0</v>
+      </c>
+      <c r="X76" s="9" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="77" spans="1:24" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="C77" s="9">
-        <f t="shared" si="8"/>
+    <row r="77" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>23</v>
+      </c>
+      <c r="C77">
+        <f t="shared" ref="C77:C82" si="10">C76+1</f>
         <v>76</v>
       </c>
-      <c r="D77" s="9" t="s">
-        <v>153</v>
-      </c>
-      <c r="E77" s="9" t="str">
-        <f t="shared" si="9"/>
-        <v>76 GICS-beta2m (beta3m)</v>
-      </c>
-      <c r="F77" s="9" t="s">
-        <v>155</v>
-      </c>
-      <c r="G77" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="H77" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="K77" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="L77" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="M77" s="9">
-        <v>0.1</v>
-      </c>
-      <c r="N77" s="9">
+      <c r="E77" t="str">
+        <f t="shared" ref="E77:E82" si="11">TEXT(C77,"00") &amp; " Sector2-"&amp;K77&amp;" ("&amp;Q77&amp;IF(P77&lt;&gt;"","+ ","")&amp;P77&amp;")"</f>
+        <v>76 Sector2-beta3m (beta3m+ Longi.beta3m&gt;2.5)</v>
+      </c>
+      <c r="F77" t="s">
+        <v>159</v>
+      </c>
+      <c r="G77" t="s">
+        <v>158</v>
+      </c>
+      <c r="H77" t="s">
+        <v>26</v>
+      </c>
+      <c r="K77" t="s">
+        <v>27</v>
+      </c>
+      <c r="L77" t="s">
+        <v>28</v>
+      </c>
+      <c r="M77">
+        <v>0.1</v>
+      </c>
+      <c r="N77">
         <v>10</v>
       </c>
-      <c r="O77" s="9">
-        <v>4</v>
-      </c>
-      <c r="Q77" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="R77" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="S77" s="13" t="s">
-        <v>154</v>
-      </c>
-      <c r="T77" s="9">
-        <v>3</v>
-      </c>
-      <c r="U77" s="9">
-        <v>0</v>
-      </c>
-      <c r="V77" s="9">
-        <v>20</v>
-      </c>
-      <c r="W77" s="9">
-        <v>0</v>
-      </c>
-      <c r="X77" s="9" t="s">
-        <v>135</v>
+      <c r="O77">
+        <v>4</v>
+      </c>
+      <c r="P77" t="s">
+        <v>143</v>
+      </c>
+      <c r="Q77" t="s">
+        <v>27</v>
+      </c>
+      <c r="R77" t="s">
+        <v>28</v>
+      </c>
+      <c r="S77">
+        <v>1</v>
+      </c>
+      <c r="T77">
+        <v>3</v>
+      </c>
+      <c r="U77">
+        <v>0</v>
+      </c>
+      <c r="V77">
+        <v>20</v>
+      </c>
+      <c r="W77">
+        <v>0</v>
+      </c>
+      <c r="X77" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="78" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A78" t="s">
-        <v>23</v>
-      </c>
       <c r="C78">
-        <f>C77+1</f>
+        <f t="shared" si="10"/>
         <v>77</v>
       </c>
       <c r="E78" t="str">
-        <f>TEXT(C78,"00") &amp; " Sector2-"&amp;K78&amp;" ("&amp;Q78&amp;IF(P78&lt;&gt;"","+ ","")&amp;P78&amp;")"</f>
-        <v>77 Sector2-beta3m (beta3m+ Longi.beta3m&gt;2.5)</v>
+        <f t="shared" si="11"/>
+        <v>77 Sector2-quot2050 (beta3m+ Longi.beta3m&gt;2.5)</v>
       </c>
       <c r="F78" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G78" t="s">
         <v>158</v>
@@ -5522,7 +5519,7 @@
         <v>26</v>
       </c>
       <c r="K78" t="s">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="L78" t="s">
         <v>28</v>
@@ -5565,16 +5562,16 @@
       </c>
     </row>
     <row r="79" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A79" t="s">
-        <v>23</v>
-      </c>
       <c r="C79">
-        <f>C78+1</f>
+        <f t="shared" si="10"/>
         <v>78</v>
       </c>
       <c r="E79" t="str">
-        <f>TEXT(C79,"00") &amp; " Sector2-"&amp;K79&amp;" ("&amp;Q79&amp;IF(P79&lt;&gt;"","+ ","")&amp;P79&amp;")"</f>
-        <v>78 Sector2-quot2050 (beta3m+ Longi.beta3m&gt;2.5)</v>
+        <f t="shared" si="11"/>
+        <v>78 Sector2-beta3m (beta3m)</v>
+      </c>
+      <c r="F79" t="s">
+        <v>159</v>
       </c>
       <c r="G79" t="s">
         <v>158</v>
@@ -5583,7 +5580,7 @@
         <v>26</v>
       </c>
       <c r="K79" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="L79" t="s">
         <v>28</v>
@@ -5597,9 +5594,6 @@
       <c r="O79">
         <v>4</v>
       </c>
-      <c r="P79" t="s">
-        <v>143</v>
-      </c>
       <c r="Q79" t="s">
         <v>27</v>
       </c>
@@ -5626,16 +5620,16 @@
       </c>
     </row>
     <row r="80" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A80" t="s">
-        <v>23</v>
-      </c>
       <c r="C80">
-        <f>C79+1</f>
+        <f t="shared" si="10"/>
         <v>79</v>
       </c>
       <c r="E80" t="str">
-        <f>TEXT(C80,"00") &amp; " Sector2-"&amp;K80&amp;" ("&amp;Q80&amp;IF(P80&lt;&gt;"","+ ","")&amp;P80&amp;")"</f>
-        <v>79 Sector2-beta3m (beta3m)</v>
+        <f t="shared" si="11"/>
+        <v>79 Sector2-quot2050 (beta3m)</v>
+      </c>
+      <c r="F80" t="s">
+        <v>160</v>
       </c>
       <c r="G80" t="s">
         <v>158</v>
@@ -5644,7 +5638,7 @@
         <v>26</v>
       </c>
       <c r="K80" t="s">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="L80" t="s">
         <v>28</v>
@@ -5684,16 +5678,16 @@
       </c>
     </row>
     <row r="81" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A81" t="s">
-        <v>23</v>
-      </c>
       <c r="C81">
-        <f>C80+1</f>
+        <f t="shared" si="10"/>
         <v>80</v>
       </c>
       <c r="E81" t="str">
-        <f>TEXT(C81,"00") &amp; " Sector2-"&amp;K81&amp;" ("&amp;Q81&amp;IF(P81&lt;&gt;"","+ ","")&amp;P81&amp;")"</f>
-        <v>80 Sector2-quot2050 (beta3m)</v>
+        <f t="shared" si="11"/>
+        <v>80 Sector2-sh3m (beta3m+ Longi.beta3m&gt;2.5)</v>
+      </c>
+      <c r="F81" t="s">
+        <v>161</v>
       </c>
       <c r="G81" t="s">
         <v>158</v>
@@ -5702,7 +5696,7 @@
         <v>26</v>
       </c>
       <c r="K81" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="L81" t="s">
         <v>28</v>
@@ -5716,6 +5710,9 @@
       <c r="O81">
         <v>4</v>
       </c>
+      <c r="P81" t="s">
+        <v>143</v>
+      </c>
       <c r="Q81" t="s">
         <v>27</v>
       </c>
@@ -5739,6 +5736,67 @@
       </c>
       <c r="X81" t="s">
         <v>135</v>
+      </c>
+    </row>
+    <row r="82" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>23</v>
+      </c>
+      <c r="C82">
+        <f t="shared" si="10"/>
+        <v>81</v>
+      </c>
+      <c r="E82" t="str">
+        <f t="shared" si="11"/>
+        <v>81 Sector2-sh3m (beta3m)</v>
+      </c>
+      <c r="F82" t="s">
+        <v>161</v>
+      </c>
+      <c r="G82" t="s">
+        <v>158</v>
+      </c>
+      <c r="H82" t="s">
+        <v>26</v>
+      </c>
+      <c r="K82" t="s">
+        <v>34</v>
+      </c>
+      <c r="L82" t="s">
+        <v>28</v>
+      </c>
+      <c r="M82">
+        <v>0.1</v>
+      </c>
+      <c r="N82">
+        <v>10</v>
+      </c>
+      <c r="O82">
+        <v>4</v>
+      </c>
+      <c r="Q82" t="s">
+        <v>27</v>
+      </c>
+      <c r="R82" t="s">
+        <v>28</v>
+      </c>
+      <c r="S82">
+        <v>1</v>
+      </c>
+      <c r="T82">
+        <v>3</v>
+      </c>
+      <c r="U82">
+        <v>0</v>
+      </c>
+      <c r="V82">
+        <v>20</v>
+      </c>
+      <c r="W82">
+        <v>0</v>
+      </c>
+      <c r="X82" t="s">
+        <v>163</v>
       </c>
     </row>
   </sheetData>

--- a/strategy_grp2/app/control/control_board.xlsx
+++ b/strategy_grp2/app/control/control_board.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\Gandalf\sm-home\potentials\strategy_grp2\app\control\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9098EDB7-00C0-4EA8-9E2F-681F232E7EB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43757540-4C32-494E-87FD-39D8DC3092DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25920" yWindow="1020" windowWidth="28935" windowHeight="14355" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="255" yWindow="810" windowWidth="34320" windowHeight="14355" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Runs" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="828" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="863" uniqueCount="172">
   <si>
     <t>D</t>
   </si>
@@ -456,9 +456,6 @@
     <t>Longi.beta3m&gt;2.5</t>
   </si>
   <si>
-    <t>Longi.beta3m&gt;3</t>
-  </si>
-  <si>
     <t>næstbedst LON, men kun halvt så god som beta-baseret</t>
   </si>
   <si>
@@ -495,9 +492,6 @@
     <t>Næsten som 02</t>
   </si>
   <si>
-    <t>Basis</t>
-  </si>
-  <si>
     <t>Stamdata.Sector2</t>
   </si>
   <si>
@@ -514,6 +508,36 @@
   </si>
   <si>
     <t>rank, per1d,per5d,per10d</t>
+  </si>
+  <si>
+    <t>Rimelig (kun GICS=Tech blev valgt)</t>
+  </si>
+  <si>
+    <t>Longi.beta3m&gt;2</t>
+  </si>
+  <si>
+    <t>Kun 3 pr grp for bredere udvalg</t>
+  </si>
+  <si>
+    <t>Bytte priority-metode</t>
+  </si>
+  <si>
+    <t>giver kun tab.  Beta er bedst til prioritering</t>
+  </si>
+  <si>
+    <t>Mindre god, men bedst Sector2</t>
+  </si>
+  <si>
+    <t>Old basis</t>
+  </si>
+  <si>
+    <t>Ny basis, men 3 udvalg er bedre</t>
+  </si>
+  <si>
+    <t>Bedst (men 4 i udvalg giver for mange)</t>
+  </si>
+  <si>
+    <t>Ny (3 i udvalg)</t>
   </si>
 </sst>
 </file>
@@ -954,7 +978,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Y82"/>
+  <dimension ref="A1:Y86"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
@@ -975,10 +999,10 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>151</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>152</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>2</v>
@@ -1048,21 +1072,18 @@
       <c r="A2" t="s">
         <v>23</v>
       </c>
-      <c r="B2" t="s">
-        <v>23</v>
-      </c>
       <c r="C2">
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>157</v>
+        <v>168</v>
       </c>
       <c r="E2" t="str">
         <f>TEXT(C2,"00") &amp; " GICS-"&amp;K2&amp;" ("&amp;Q2&amp;IF(P2&lt;&gt;"","+ ","")&amp;P2&amp;")"</f>
         <v>01 GICS-beta3m (beta3m+ Longi.beta3m&gt;2.5)</v>
       </c>
       <c r="F2" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="G2" t="s">
         <v>25</v>
@@ -1110,7 +1131,7 @@
         <v>0</v>
       </c>
       <c r="X2" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="3" spans="1:25" x14ac:dyDescent="0.25">
@@ -1123,7 +1144,7 @@
         <v>02 GICS-beta3m (beta3m)</v>
       </c>
       <c r="F3" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="G3" t="s">
         <v>25</v>
@@ -1168,7 +1189,7 @@
         <v>0</v>
       </c>
       <c r="X3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="4" spans="1:25" x14ac:dyDescent="0.25">
@@ -1239,7 +1260,7 @@
       </c>
       <c r="E5" t="str">
         <f t="shared" si="2"/>
-        <v>04 GICS-rank (beta3m+ Longi.beta3m&gt;3)</v>
+        <v>04 GICS-rank (beta3m+ Longi.beta3m&gt;2.5)</v>
       </c>
       <c r="F5" t="s">
         <v>30</v>
@@ -1266,7 +1287,7 @@
         <v>4</v>
       </c>
       <c r="P5" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="Q5" t="s">
         <v>27</v>
@@ -1352,19 +1373,19 @@
       </c>
     </row>
     <row r="7" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>23</v>
-      </c>
       <c r="C7">
         <f t="shared" si="3"/>
         <v>6</v>
       </c>
+      <c r="D7" t="s">
+        <v>169</v>
+      </c>
       <c r="E7" t="str">
         <f t="shared" si="2"/>
         <v>06 GICS-sh3m (beta3m)</v>
       </c>
       <c r="F7" t="s">
-        <v>24</v>
+        <v>170</v>
       </c>
       <c r="G7" t="s">
         <v>25</v>
@@ -1409,7 +1430,7 @@
         <v>0</v>
       </c>
       <c r="X7" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="8" spans="1:25" x14ac:dyDescent="0.25">
@@ -3457,7 +3478,7 @@
         <v>43 GICS-rank (beta3m)</v>
       </c>
       <c r="F44" s="11" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G44" s="11" t="s">
         <v>131</v>
@@ -4223,7 +4244,7 @@
         <v>56 GICS-beta3m (beta3m+ Longi.beta3m&gt;2.5)</v>
       </c>
       <c r="F57" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G57" t="s">
         <v>25</v>
@@ -4284,7 +4305,7 @@
         <v>57 GICS-beta3m (beta3m+ Longi.beta3m&gt;2.5)</v>
       </c>
       <c r="F58" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G58" t="s">
         <v>25</v>
@@ -4345,7 +4366,7 @@
         <v>58 GICS-beta3m (beta3m+ Longi.beta3m&gt;2.5)</v>
       </c>
       <c r="F59" s="9" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G59" s="9" t="s">
         <v>25</v>
@@ -4406,7 +4427,7 @@
         <v>59 GICS-beta3m (beta3m+ Longi.beta3m&gt;2.5)</v>
       </c>
       <c r="F60" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="G60" t="s">
         <v>25</v>
@@ -4467,7 +4488,7 @@
         <v>60 GICS-beta3m (beta3m+ Longi.beta3m&gt;2.5)</v>
       </c>
       <c r="F61" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="G61" t="s">
         <v>25</v>
@@ -4528,7 +4549,7 @@
         <v>61 GICS-beta3m (beta3m+ Longi.beta3m&gt;2.5)</v>
       </c>
       <c r="F62" s="9" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="G62" s="9" t="s">
         <v>25</v>
@@ -4589,7 +4610,7 @@
         <v>62 GICS-beta3m (beta3m+ Longi.rank&lt;1000)</v>
       </c>
       <c r="F63" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="G63" t="s">
         <v>25</v>
@@ -4637,7 +4658,7 @@
         <v>0</v>
       </c>
       <c r="X63" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="64" spans="3:24" x14ac:dyDescent="0.25">
@@ -4650,7 +4671,7 @@
         <v>63 GICS-beta3m (beta3m+ Longi.beta3m&gt;2.5)</v>
       </c>
       <c r="F64" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="G64" t="s">
         <v>25</v>
@@ -4698,7 +4719,7 @@
         <v>0</v>
       </c>
       <c r="X64" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="65" spans="1:24" x14ac:dyDescent="0.25">
@@ -4711,7 +4732,7 @@
         <v>64 GICS-beta3m (beta3m+ Longi.rank&lt;1000)</v>
       </c>
       <c r="F65" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="G65" t="s">
         <v>25</v>
@@ -4759,7 +4780,7 @@
         <v>0</v>
       </c>
       <c r="X65" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="66" spans="1:24" x14ac:dyDescent="0.25">
@@ -4772,7 +4793,7 @@
         <v>65 GICS-beta3m (beta3m+ Longi.beta3m&gt;2.5)</v>
       </c>
       <c r="F66" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="G66" t="s">
         <v>25</v>
@@ -4820,7 +4841,7 @@
         <v>0</v>
       </c>
       <c r="X66" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="67" spans="1:24" x14ac:dyDescent="0.25">
@@ -4833,7 +4854,7 @@
         <v>66 GICS-beta3m (beta3m)</v>
       </c>
       <c r="F67" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="G67" t="s">
         <v>25</v>
@@ -4878,7 +4899,7 @@
         <v>0</v>
       </c>
       <c r="X67" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="68" spans="1:24" x14ac:dyDescent="0.25">
@@ -4891,7 +4912,7 @@
         <v>67 GICS-beta3m (beta3m+ Longi.rank&lt;1000 .and. Longi.beta3m&gt;2.5)</v>
       </c>
       <c r="F68" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="G68" t="s">
         <v>25</v>
@@ -4915,7 +4936,7 @@
         <v>4</v>
       </c>
       <c r="P68" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="Q68" t="s">
         <v>27</v>
@@ -4939,7 +4960,7 @@
         <v>0</v>
       </c>
       <c r="X68" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="69" spans="1:24" s="9" customFormat="1" x14ac:dyDescent="0.25">
@@ -4952,7 +4973,7 @@
         <v>68 GICS-beta3m (beta3m+ Longi.rank&lt;1000 .and. Longi.beta3m&gt;2.5)</v>
       </c>
       <c r="F69" s="9" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="G69" s="9" t="s">
         <v>25</v>
@@ -4976,7 +4997,7 @@
         <v>5</v>
       </c>
       <c r="P69" s="9" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="Q69" s="9" t="s">
         <v>27</v>
@@ -5000,7 +5021,7 @@
         <v>0</v>
       </c>
       <c r="X69" s="9" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="70" spans="1:24" x14ac:dyDescent="0.25">
@@ -5009,14 +5030,14 @@
         <v>69</v>
       </c>
       <c r="D70" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E70" t="str">
         <f t="shared" si="5"/>
         <v>69 GICS-beta2m (beta3m+ Longi.beta3m&gt;2.5)</v>
       </c>
       <c r="F70" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G70" t="s">
         <v>25</v>
@@ -5073,14 +5094,14 @@
         <v>70</v>
       </c>
       <c r="D71" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E71" t="str">
         <f t="shared" si="5"/>
         <v>70 GICS-beta1m (beta3m+ Longi.beta3m&gt;2.5)</v>
       </c>
       <c r="F71" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G71" t="s">
         <v>25</v>
@@ -5137,14 +5158,14 @@
         <v>71</v>
       </c>
       <c r="D72" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E72" t="str">
         <f t="shared" ref="E72:E73" si="6">TEXT(C72,"00") &amp; " GICS-"&amp;K72&amp;" ("&amp;Q72&amp;IF(P72&lt;&gt;"","+ ","")&amp;P72&amp;")"</f>
         <v>71 GICS-beta2m (beta3m)</v>
       </c>
       <c r="F72" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G72" t="s">
         <v>25</v>
@@ -5198,14 +5219,14 @@
         <v>72</v>
       </c>
       <c r="D73" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E73" t="str">
         <f t="shared" si="6"/>
         <v>72 GICS-beta1m (beta3m)</v>
       </c>
       <c r="F73" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G73" t="s">
         <v>25</v>
@@ -5259,14 +5280,14 @@
         <v>73</v>
       </c>
       <c r="D74" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E74" t="str">
         <f t="shared" ref="E74" si="7">TEXT(C74,"00") &amp; " GICS-"&amp;K74&amp;" ("&amp;Q74&amp;IF(P74&lt;&gt;"","+ ","")&amp;P74&amp;")"</f>
         <v>73 GICS-beta2m (beta3m)</v>
       </c>
       <c r="F74" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G74" t="s">
         <v>25</v>
@@ -5316,18 +5337,18 @@
     </row>
     <row r="75" spans="1:24" x14ac:dyDescent="0.25">
       <c r="C75">
-        <f t="shared" ref="C75:C76" si="8">C74+1</f>
+        <f t="shared" ref="C75:C86" si="8">C74+1</f>
         <v>74</v>
       </c>
       <c r="D75" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E75" t="str">
-        <f t="shared" ref="E75:E76" si="9">TEXT(C75,"00") &amp; " GICS-"&amp;K75&amp;" ("&amp;Q75&amp;IF(P75&lt;&gt;"","+ ","")&amp;P75&amp;")"</f>
+        <f t="shared" ref="E75:E80" si="9">TEXT(C75,"00") &amp; " GICS-"&amp;K75&amp;" ("&amp;Q75&amp;IF(P75&lt;&gt;"","+ ","")&amp;P75&amp;")"</f>
         <v>74 GICS-beta2m (beta3m)</v>
       </c>
       <c r="F75" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G75" t="s">
         <v>25</v>
@@ -5381,14 +5402,14 @@
         <v>75</v>
       </c>
       <c r="D76" s="9" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E76" s="9" t="str">
         <f t="shared" si="9"/>
         <v>75 GICS-beta2m (beta3m)</v>
       </c>
       <c r="F76" s="9" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G76" s="9" t="s">
         <v>25</v>
@@ -5418,7 +5439,7 @@
         <v>28</v>
       </c>
       <c r="S76" s="9" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="T76" s="9">
         <v>3</v>
@@ -5437,144 +5458,147 @@
       </c>
     </row>
     <row r="77" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A77" t="s">
+      <c r="C77">
+        <f t="shared" si="8"/>
+        <v>76</v>
+      </c>
+      <c r="E77" t="str">
+        <f t="shared" si="9"/>
+        <v>76 GICS-beta3m (beta3m)</v>
+      </c>
+      <c r="F77" t="s">
+        <v>164</v>
+      </c>
+      <c r="G77" t="s">
+        <v>25</v>
+      </c>
+      <c r="H77" t="s">
+        <v>26</v>
+      </c>
+      <c r="K77" t="s">
+        <v>27</v>
+      </c>
+      <c r="L77" t="s">
+        <v>28</v>
+      </c>
+      <c r="M77">
+        <v>0.1</v>
+      </c>
+      <c r="N77">
+        <v>10</v>
+      </c>
+      <c r="O77">
+        <v>3</v>
+      </c>
+      <c r="Q77" t="s">
+        <v>27</v>
+      </c>
+      <c r="R77" t="s">
+        <v>28</v>
+      </c>
+      <c r="S77">
+        <v>1</v>
+      </c>
+      <c r="T77">
+        <v>3</v>
+      </c>
+      <c r="U77">
+        <v>0</v>
+      </c>
+      <c r="V77">
+        <v>20</v>
+      </c>
+      <c r="W77">
+        <v>0</v>
+      </c>
+      <c r="X77" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="78" spans="1:24" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A78" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="C77">
-        <f t="shared" ref="C77:C82" si="10">C76+1</f>
-        <v>76</v>
-      </c>
-      <c r="E77" t="str">
-        <f t="shared" ref="E77:E82" si="11">TEXT(C77,"00") &amp; " Sector2-"&amp;K77&amp;" ("&amp;Q77&amp;IF(P77&lt;&gt;"","+ ","")&amp;P77&amp;")"</f>
-        <v>76 Sector2-beta3m (beta3m+ Longi.beta3m&gt;2.5)</v>
-      </c>
-      <c r="F77" t="s">
-        <v>159</v>
-      </c>
-      <c r="G77" t="s">
-        <v>158</v>
-      </c>
-      <c r="H77" t="s">
-        <v>26</v>
-      </c>
-      <c r="K77" t="s">
-        <v>27</v>
-      </c>
-      <c r="L77" t="s">
-        <v>28</v>
-      </c>
-      <c r="M77">
-        <v>0.1</v>
-      </c>
-      <c r="N77">
-        <v>10</v>
-      </c>
-      <c r="O77">
-        <v>4</v>
-      </c>
-      <c r="P77" t="s">
-        <v>143</v>
-      </c>
-      <c r="Q77" t="s">
-        <v>27</v>
-      </c>
-      <c r="R77" t="s">
-        <v>28</v>
-      </c>
-      <c r="S77">
-        <v>1</v>
-      </c>
-      <c r="T77">
-        <v>3</v>
-      </c>
-      <c r="U77">
-        <v>0</v>
-      </c>
-      <c r="V77">
-        <v>20</v>
-      </c>
-      <c r="W77">
-        <v>0</v>
-      </c>
-      <c r="X77" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="78" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="C78">
-        <f t="shared" si="10"/>
+      <c r="B78" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="C78" s="9">
+        <f t="shared" si="8"/>
         <v>77</v>
       </c>
-      <c r="E78" t="str">
-        <f t="shared" si="11"/>
-        <v>77 Sector2-quot2050 (beta3m+ Longi.beta3m&gt;2.5)</v>
-      </c>
-      <c r="F78" t="s">
-        <v>160</v>
-      </c>
-      <c r="G78" t="s">
-        <v>158</v>
-      </c>
-      <c r="H78" t="s">
-        <v>26</v>
-      </c>
-      <c r="K78" t="s">
-        <v>45</v>
-      </c>
-      <c r="L78" t="s">
-        <v>28</v>
-      </c>
-      <c r="M78">
-        <v>0.1</v>
-      </c>
-      <c r="N78">
-        <v>10</v>
-      </c>
-      <c r="O78">
-        <v>4</v>
-      </c>
-      <c r="P78" t="s">
-        <v>143</v>
-      </c>
-      <c r="Q78" t="s">
-        <v>27</v>
-      </c>
-      <c r="R78" t="s">
-        <v>28</v>
-      </c>
-      <c r="S78">
-        <v>1</v>
-      </c>
-      <c r="T78">
-        <v>3</v>
-      </c>
-      <c r="U78">
-        <v>0</v>
-      </c>
-      <c r="V78">
-        <v>20</v>
-      </c>
-      <c r="W78">
-        <v>0</v>
-      </c>
-      <c r="X78" t="s">
-        <v>135</v>
+      <c r="D78" s="9" t="s">
+        <v>171</v>
+      </c>
+      <c r="E78" s="9" t="str">
+        <f t="shared" si="9"/>
+        <v>77 GICS-sh3m (beta3m)</v>
+      </c>
+      <c r="F78" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="G78" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="H78" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="K78" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="L78" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="M78" s="9">
+        <v>0.1</v>
+      </c>
+      <c r="N78" s="9">
+        <v>10</v>
+      </c>
+      <c r="O78" s="9">
+        <v>3</v>
+      </c>
+      <c r="Q78" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="R78" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="S78" s="9">
+        <v>1</v>
+      </c>
+      <c r="T78" s="9">
+        <v>3</v>
+      </c>
+      <c r="U78" s="9">
+        <v>0</v>
+      </c>
+      <c r="V78" s="9">
+        <v>20</v>
+      </c>
+      <c r="W78" s="9">
+        <v>0</v>
+      </c>
+      <c r="X78" s="9" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="79" spans="1:24" x14ac:dyDescent="0.25">
       <c r="C79">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>78</v>
       </c>
+      <c r="D79" t="s">
+        <v>165</v>
+      </c>
       <c r="E79" t="str">
-        <f t="shared" si="11"/>
-        <v>78 Sector2-beta3m (beta3m)</v>
+        <f t="shared" si="9"/>
+        <v>78 GICS-beta3m (sh3m)</v>
       </c>
       <c r="F79" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="G79" t="s">
-        <v>158</v>
+        <v>25</v>
       </c>
       <c r="H79" t="s">
         <v>26</v>
@@ -5595,7 +5619,7 @@
         <v>4</v>
       </c>
       <c r="Q79" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="R79" t="s">
         <v>28</v>
@@ -5616,187 +5640,428 @@
         <v>0</v>
       </c>
       <c r="X79" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="80" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="C80">
-        <f t="shared" si="10"/>
+        <v>161</v>
+      </c>
+    </row>
+    <row r="80" spans="1:24" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="C80" s="9">
+        <f t="shared" si="8"/>
         <v>79</v>
       </c>
-      <c r="E80" t="str">
-        <f t="shared" si="11"/>
-        <v>79 Sector2-quot2050 (beta3m)</v>
-      </c>
-      <c r="F80" t="s">
-        <v>160</v>
-      </c>
-      <c r="G80" t="s">
-        <v>158</v>
-      </c>
-      <c r="H80" t="s">
-        <v>26</v>
-      </c>
-      <c r="K80" t="s">
-        <v>45</v>
-      </c>
-      <c r="L80" t="s">
-        <v>28</v>
-      </c>
-      <c r="M80">
-        <v>0.1</v>
-      </c>
-      <c r="N80">
-        <v>10</v>
-      </c>
-      <c r="O80">
-        <v>4</v>
-      </c>
-      <c r="Q80" t="s">
-        <v>27</v>
-      </c>
-      <c r="R80" t="s">
-        <v>28</v>
-      </c>
-      <c r="S80">
-        <v>1</v>
-      </c>
-      <c r="T80">
-        <v>3</v>
-      </c>
-      <c r="U80">
-        <v>0</v>
-      </c>
-      <c r="V80">
-        <v>20</v>
-      </c>
-      <c r="W80">
-        <v>0</v>
-      </c>
-      <c r="X80" t="s">
-        <v>135</v>
+      <c r="D80" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="E80" s="9" t="str">
+        <f t="shared" si="9"/>
+        <v>79 GICS-sh3m (sh3m)</v>
+      </c>
+      <c r="F80" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="G80" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="H80" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="K80" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="L80" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="M80" s="9">
+        <v>0.1</v>
+      </c>
+      <c r="N80" s="9">
+        <v>10</v>
+      </c>
+      <c r="O80" s="9">
+        <v>4</v>
+      </c>
+      <c r="Q80" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="R80" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="S80" s="9">
+        <v>1</v>
+      </c>
+      <c r="T80" s="9">
+        <v>3</v>
+      </c>
+      <c r="U80" s="9">
+        <v>0</v>
+      </c>
+      <c r="V80" s="9">
+        <v>20</v>
+      </c>
+      <c r="W80" s="9">
+        <v>0</v>
+      </c>
+      <c r="X80" s="9" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="81" spans="1:24" x14ac:dyDescent="0.25">
       <c r="C81">
+        <f t="shared" si="8"/>
+        <v>80</v>
+      </c>
+      <c r="E81" t="str">
+        <f t="shared" ref="E81:E86" si="10">TEXT(C81,"00") &amp; " Sector2-"&amp;K81&amp;" ("&amp;Q81&amp;IF(P81&lt;&gt;"","+ ","")&amp;P81&amp;")"</f>
+        <v>80 Sector2-beta3m (beta3m+ Longi.beta3m&gt;2)</v>
+      </c>
+      <c r="F81" t="s">
+        <v>162</v>
+      </c>
+      <c r="G81" t="s">
+        <v>156</v>
+      </c>
+      <c r="H81" t="s">
+        <v>26</v>
+      </c>
+      <c r="K81" t="s">
+        <v>27</v>
+      </c>
+      <c r="L81" t="s">
+        <v>28</v>
+      </c>
+      <c r="M81">
+        <v>0.1</v>
+      </c>
+      <c r="N81">
+        <v>10</v>
+      </c>
+      <c r="O81">
+        <v>4</v>
+      </c>
+      <c r="P81" t="s">
+        <v>163</v>
+      </c>
+      <c r="Q81" t="s">
+        <v>27</v>
+      </c>
+      <c r="R81" t="s">
+        <v>28</v>
+      </c>
+      <c r="S81">
+        <v>1</v>
+      </c>
+      <c r="T81">
+        <v>3</v>
+      </c>
+      <c r="U81">
+        <v>0</v>
+      </c>
+      <c r="V81">
+        <v>20</v>
+      </c>
+      <c r="W81">
+        <v>0</v>
+      </c>
+      <c r="X81" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="82" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="C82">
+        <f t="shared" si="8"/>
+        <v>81</v>
+      </c>
+      <c r="E82" t="str">
         <f t="shared" si="10"/>
-        <v>80</v>
-      </c>
-      <c r="E81" t="str">
-        <f t="shared" si="11"/>
-        <v>80 Sector2-sh3m (beta3m+ Longi.beta3m&gt;2.5)</v>
-      </c>
-      <c r="F81" t="s">
+        <v>81 Sector2-quot2050 (beta3m+ Longi.beta3m&gt;2)</v>
+      </c>
+      <c r="F82" t="s">
+        <v>158</v>
+      </c>
+      <c r="G82" t="s">
+        <v>156</v>
+      </c>
+      <c r="H82" t="s">
+        <v>26</v>
+      </c>
+      <c r="K82" t="s">
+        <v>45</v>
+      </c>
+      <c r="L82" t="s">
+        <v>28</v>
+      </c>
+      <c r="M82">
+        <v>0.1</v>
+      </c>
+      <c r="N82">
+        <v>10</v>
+      </c>
+      <c r="O82">
+        <v>4</v>
+      </c>
+      <c r="P82" t="s">
+        <v>163</v>
+      </c>
+      <c r="Q82" t="s">
+        <v>27</v>
+      </c>
+      <c r="R82" t="s">
+        <v>28</v>
+      </c>
+      <c r="S82">
+        <v>1</v>
+      </c>
+      <c r="T82">
+        <v>3</v>
+      </c>
+      <c r="U82">
+        <v>0</v>
+      </c>
+      <c r="V82">
+        <v>20</v>
+      </c>
+      <c r="W82">
+        <v>0</v>
+      </c>
+      <c r="X82" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="83" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="C83">
+        <f t="shared" si="8"/>
+        <v>82</v>
+      </c>
+      <c r="E83" t="str">
+        <f t="shared" si="10"/>
+        <v>82 Sector2-beta3m (beta3m)</v>
+      </c>
+      <c r="F83" t="s">
+        <v>157</v>
+      </c>
+      <c r="G83" t="s">
+        <v>156</v>
+      </c>
+      <c r="H83" t="s">
+        <v>26</v>
+      </c>
+      <c r="K83" t="s">
+        <v>27</v>
+      </c>
+      <c r="L83" t="s">
+        <v>28</v>
+      </c>
+      <c r="M83">
+        <v>0.1</v>
+      </c>
+      <c r="N83">
+        <v>10</v>
+      </c>
+      <c r="O83">
+        <v>4</v>
+      </c>
+      <c r="Q83" t="s">
+        <v>27</v>
+      </c>
+      <c r="R83" t="s">
+        <v>28</v>
+      </c>
+      <c r="S83">
+        <v>1</v>
+      </c>
+      <c r="T83">
+        <v>3</v>
+      </c>
+      <c r="U83">
+        <v>0</v>
+      </c>
+      <c r="V83">
+        <v>20</v>
+      </c>
+      <c r="W83">
+        <v>0</v>
+      </c>
+      <c r="X83" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="84" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="C84">
+        <f t="shared" si="8"/>
+        <v>83</v>
+      </c>
+      <c r="E84" t="str">
+        <f t="shared" si="10"/>
+        <v>83 Sector2-quot2050 (beta3m)</v>
+      </c>
+      <c r="F84" t="s">
+        <v>158</v>
+      </c>
+      <c r="G84" t="s">
+        <v>156</v>
+      </c>
+      <c r="H84" t="s">
+        <v>26</v>
+      </c>
+      <c r="K84" t="s">
+        <v>45</v>
+      </c>
+      <c r="L84" t="s">
+        <v>28</v>
+      </c>
+      <c r="M84">
+        <v>0.1</v>
+      </c>
+      <c r="N84">
+        <v>10</v>
+      </c>
+      <c r="O84">
+        <v>4</v>
+      </c>
+      <c r="Q84" t="s">
+        <v>27</v>
+      </c>
+      <c r="R84" t="s">
+        <v>28</v>
+      </c>
+      <c r="S84">
+        <v>1</v>
+      </c>
+      <c r="T84">
+        <v>3</v>
+      </c>
+      <c r="U84">
+        <v>0</v>
+      </c>
+      <c r="V84">
+        <v>20</v>
+      </c>
+      <c r="W84">
+        <v>0</v>
+      </c>
+      <c r="X84" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="85" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>23</v>
+      </c>
+      <c r="C85">
+        <f t="shared" si="8"/>
+        <v>84</v>
+      </c>
+      <c r="E85" t="str">
+        <f t="shared" si="10"/>
+        <v>84 Sector2-sh3m (beta3m+ Longi.beta3m&gt;2)</v>
+      </c>
+      <c r="F85" t="s">
+        <v>167</v>
+      </c>
+      <c r="G85" t="s">
+        <v>156</v>
+      </c>
+      <c r="H85" t="s">
+        <v>26</v>
+      </c>
+      <c r="K85" t="s">
+        <v>34</v>
+      </c>
+      <c r="L85" t="s">
+        <v>28</v>
+      </c>
+      <c r="M85">
+        <v>0.1</v>
+      </c>
+      <c r="N85">
+        <v>10</v>
+      </c>
+      <c r="O85">
+        <v>4</v>
+      </c>
+      <c r="P85" t="s">
+        <v>163</v>
+      </c>
+      <c r="Q85" t="s">
+        <v>27</v>
+      </c>
+      <c r="R85" t="s">
+        <v>28</v>
+      </c>
+      <c r="S85">
+        <v>1</v>
+      </c>
+      <c r="T85">
+        <v>3</v>
+      </c>
+      <c r="U85">
+        <v>0</v>
+      </c>
+      <c r="V85">
+        <v>20</v>
+      </c>
+      <c r="W85">
+        <v>0</v>
+      </c>
+      <c r="X85" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="86" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="C86">
+        <f t="shared" si="8"/>
+        <v>85</v>
+      </c>
+      <c r="E86" t="str">
+        <f t="shared" si="10"/>
+        <v>85 Sector2-sh3m (beta3m)</v>
+      </c>
+      <c r="F86" t="s">
+        <v>159</v>
+      </c>
+      <c r="G86" t="s">
+        <v>156</v>
+      </c>
+      <c r="H86" t="s">
+        <v>26</v>
+      </c>
+      <c r="K86" t="s">
+        <v>34</v>
+      </c>
+      <c r="L86" t="s">
+        <v>28</v>
+      </c>
+      <c r="M86">
+        <v>0.1</v>
+      </c>
+      <c r="N86">
+        <v>10</v>
+      </c>
+      <c r="O86">
+        <v>4</v>
+      </c>
+      <c r="Q86" t="s">
+        <v>27</v>
+      </c>
+      <c r="R86" t="s">
+        <v>28</v>
+      </c>
+      <c r="S86">
+        <v>1</v>
+      </c>
+      <c r="T86">
+        <v>3</v>
+      </c>
+      <c r="U86">
+        <v>0</v>
+      </c>
+      <c r="V86">
+        <v>20</v>
+      </c>
+      <c r="W86">
+        <v>0</v>
+      </c>
+      <c r="X86" t="s">
         <v>161</v>
-      </c>
-      <c r="G81" t="s">
-        <v>158</v>
-      </c>
-      <c r="H81" t="s">
-        <v>26</v>
-      </c>
-      <c r="K81" t="s">
-        <v>34</v>
-      </c>
-      <c r="L81" t="s">
-        <v>28</v>
-      </c>
-      <c r="M81">
-        <v>0.1</v>
-      </c>
-      <c r="N81">
-        <v>10</v>
-      </c>
-      <c r="O81">
-        <v>4</v>
-      </c>
-      <c r="P81" t="s">
-        <v>143</v>
-      </c>
-      <c r="Q81" t="s">
-        <v>27</v>
-      </c>
-      <c r="R81" t="s">
-        <v>28</v>
-      </c>
-      <c r="S81">
-        <v>1</v>
-      </c>
-      <c r="T81">
-        <v>3</v>
-      </c>
-      <c r="U81">
-        <v>0</v>
-      </c>
-      <c r="V81">
-        <v>20</v>
-      </c>
-      <c r="W81">
-        <v>0</v>
-      </c>
-      <c r="X81" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="82" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A82" t="s">
-        <v>23</v>
-      </c>
-      <c r="C82">
-        <f t="shared" si="10"/>
-        <v>81</v>
-      </c>
-      <c r="E82" t="str">
-        <f t="shared" si="11"/>
-        <v>81 Sector2-sh3m (beta3m)</v>
-      </c>
-      <c r="F82" t="s">
-        <v>161</v>
-      </c>
-      <c r="G82" t="s">
-        <v>158</v>
-      </c>
-      <c r="H82" t="s">
-        <v>26</v>
-      </c>
-      <c r="K82" t="s">
-        <v>34</v>
-      </c>
-      <c r="L82" t="s">
-        <v>28</v>
-      </c>
-      <c r="M82">
-        <v>0.1</v>
-      </c>
-      <c r="N82">
-        <v>10</v>
-      </c>
-      <c r="O82">
-        <v>4</v>
-      </c>
-      <c r="Q82" t="s">
-        <v>27</v>
-      </c>
-      <c r="R82" t="s">
-        <v>28</v>
-      </c>
-      <c r="S82">
-        <v>1</v>
-      </c>
-      <c r="T82">
-        <v>3</v>
-      </c>
-      <c r="U82">
-        <v>0</v>
-      </c>
-      <c r="V82">
-        <v>20</v>
-      </c>
-      <c r="W82">
-        <v>0</v>
-      </c>
-      <c r="X82" t="s">
-        <v>163</v>
       </c>
     </row>
   </sheetData>

--- a/strategy_grp2/app/control/control_board.xlsx
+++ b/strategy_grp2/app/control/control_board.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\Gandalf\sm-home\potentials\strategy_grp2\app\control\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43757540-4C32-494E-87FD-39D8DC3092DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DAC5DF6-E4CA-4DDF-ACE1-E612649214EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="255" yWindow="810" windowWidth="34320" windowHeight="14355" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="1545" windowWidth="33900" windowHeight="14565" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Runs" sheetId="1" r:id="rId1"/>
@@ -531,13 +531,13 @@
     <t>Old basis</t>
   </si>
   <si>
-    <t>Ny basis, men 3 udvalg er bedre</t>
-  </si>
-  <si>
     <t>Bedst (men 4 i udvalg giver for mange)</t>
   </si>
   <si>
-    <t>Ny (3 i udvalg)</t>
+    <t>Ny basic</t>
+  </si>
+  <si>
+    <t>Sector2</t>
   </si>
 </sst>
 </file>
@@ -566,7 +566,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -611,6 +611,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -660,7 +666,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -675,6 +681,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1377,15 +1385,12 @@
         <f t="shared" si="3"/>
         <v>6</v>
       </c>
-      <c r="D7" t="s">
-        <v>169</v>
-      </c>
       <c r="E7" t="str">
         <f t="shared" si="2"/>
         <v>06 GICS-sh3m (beta3m)</v>
       </c>
       <c r="F7" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="G7" t="s">
         <v>25</v>
@@ -5526,8 +5531,8 @@
         <f t="shared" si="8"/>
         <v>77</v>
       </c>
-      <c r="D78" s="9" t="s">
-        <v>171</v>
+      <c r="D78" s="12" t="s">
+        <v>170</v>
       </c>
       <c r="E78" s="9" t="str">
         <f t="shared" si="9"/>
@@ -5709,6 +5714,9 @@
         <f t="shared" si="8"/>
         <v>80</v>
       </c>
+      <c r="D81" s="13" t="s">
+        <v>171</v>
+      </c>
       <c r="E81" t="str">
         <f t="shared" ref="E81:E86" si="10">TEXT(C81,"00") &amp; " Sector2-"&amp;K81&amp;" ("&amp;Q81&amp;IF(P81&lt;&gt;"","+ ","")&amp;P81&amp;")"</f>
         <v>80 Sector2-beta3m (beta3m+ Longi.beta3m&gt;2)</v>
@@ -6006,61 +6014,61 @@
         <v>135</v>
       </c>
     </row>
-    <row r="86" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="C86">
+    <row r="86" spans="1:24" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="C86" s="9">
         <f t="shared" si="8"/>
         <v>85</v>
       </c>
-      <c r="E86" t="str">
+      <c r="E86" s="9" t="str">
         <f t="shared" si="10"/>
         <v>85 Sector2-sh3m (beta3m)</v>
       </c>
-      <c r="F86" t="s">
+      <c r="F86" s="9" t="s">
         <v>159</v>
       </c>
-      <c r="G86" t="s">
+      <c r="G86" s="9" t="s">
         <v>156</v>
       </c>
-      <c r="H86" t="s">
-        <v>26</v>
-      </c>
-      <c r="K86" t="s">
+      <c r="H86" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="K86" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="L86" t="s">
-        <v>28</v>
-      </c>
-      <c r="M86">
-        <v>0.1</v>
-      </c>
-      <c r="N86">
-        <v>10</v>
-      </c>
-      <c r="O86">
-        <v>4</v>
-      </c>
-      <c r="Q86" t="s">
-        <v>27</v>
-      </c>
-      <c r="R86" t="s">
-        <v>28</v>
-      </c>
-      <c r="S86">
-        <v>1</v>
-      </c>
-      <c r="T86">
-        <v>3</v>
-      </c>
-      <c r="U86">
-        <v>0</v>
-      </c>
-      <c r="V86">
-        <v>20</v>
-      </c>
-      <c r="W86">
-        <v>0</v>
-      </c>
-      <c r="X86" t="s">
+      <c r="L86" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="M86" s="9">
+        <v>0.1</v>
+      </c>
+      <c r="N86" s="9">
+        <v>10</v>
+      </c>
+      <c r="O86" s="9">
+        <v>4</v>
+      </c>
+      <c r="Q86" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="R86" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="S86" s="9">
+        <v>1</v>
+      </c>
+      <c r="T86" s="9">
+        <v>3</v>
+      </c>
+      <c r="U86" s="9">
+        <v>0</v>
+      </c>
+      <c r="V86" s="9">
+        <v>20</v>
+      </c>
+      <c r="W86" s="9">
+        <v>0</v>
+      </c>
+      <c r="X86" s="9" t="s">
         <v>161</v>
       </c>
     </row>

--- a/strategy_grp2/app/control/control_board.xlsx
+++ b/strategy_grp2/app/control/control_board.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\Gandalf\sm-home\potentials\strategy_grp2\app\control\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DAC5DF6-E4CA-4DDF-ACE1-E612649214EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD4BA081-5347-4033-BE70-41CE2B836DD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="1545" windowWidth="33900" windowHeight="14565" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="60" yWindow="1695" windowWidth="28650" windowHeight="14565" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Runs" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="863" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="862" uniqueCount="173">
   <si>
     <t>D</t>
   </si>
@@ -538,6 +538,9 @@
   </si>
   <si>
     <t>Sector2</t>
+  </si>
+  <si>
+    <t>xxxx</t>
   </si>
 </sst>
 </file>
@@ -666,7 +669,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -682,7 +685,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1077,9 +1079,6 @@
       </c>
     </row>
     <row r="2" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>23</v>
-      </c>
       <c r="C2">
         <v>1</v>
       </c>
@@ -5709,12 +5708,12 @@
         <v>161</v>
       </c>
     </row>
-    <row r="81" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="81" spans="3:24" x14ac:dyDescent="0.25">
       <c r="C81">
         <f t="shared" si="8"/>
         <v>80</v>
       </c>
-      <c r="D81" s="13" t="s">
+      <c r="D81" t="s">
         <v>171</v>
       </c>
       <c r="E81" t="str">
@@ -5773,7 +5772,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="82" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="82" spans="3:24" x14ac:dyDescent="0.25">
       <c r="C82">
         <f t="shared" si="8"/>
         <v>81</v>
@@ -5834,7 +5833,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="83" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="83" spans="3:24" x14ac:dyDescent="0.25">
       <c r="C83">
         <f t="shared" si="8"/>
         <v>82</v>
@@ -5892,7 +5891,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="84" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="84" spans="3:24" x14ac:dyDescent="0.25">
       <c r="C84">
         <f t="shared" si="8"/>
         <v>83</v>
@@ -5950,14 +5949,14 @@
         <v>135</v>
       </c>
     </row>
-    <row r="85" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A85" t="s">
-        <v>23</v>
-      </c>
+    <row r="85" spans="3:24" x14ac:dyDescent="0.25">
       <c r="C85">
         <f t="shared" si="8"/>
         <v>84</v>
       </c>
+      <c r="D85" t="s">
+        <v>172</v>
+      </c>
       <c r="E85" t="str">
         <f t="shared" si="10"/>
         <v>84 Sector2-sh3m (beta3m+ Longi.beta3m&gt;2)</v>
@@ -6014,7 +6013,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="86" spans="1:24" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="3:24" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C86" s="9">
         <f t="shared" si="8"/>
         <v>85</v>

--- a/strategy_grp2/app/control/control_board.xlsx
+++ b/strategy_grp2/app/control/control_board.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\Gandalf\sm-home\potentials\strategy_grp2\app\control\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD4BA081-5347-4033-BE70-41CE2B836DD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{911DFE23-D83A-4E29-82A1-58B24BEDC6CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="60" yWindow="1695" windowWidth="28650" windowHeight="14565" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="1665" windowWidth="28770" windowHeight="13965" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Runs" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="862" uniqueCount="173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="882" uniqueCount="177">
   <si>
     <t>D</t>
   </si>
@@ -541,6 +541,18 @@
   </si>
   <si>
     <t>xxxx</t>
+  </si>
+  <si>
+    <t>Longi.sh3m&gt;0</t>
+  </si>
+  <si>
+    <t>Longi.sh3m&gt;2</t>
+  </si>
+  <si>
+    <t>do.</t>
+  </si>
+  <si>
+    <t>4 per gruppe for få nok</t>
   </si>
 </sst>
 </file>
@@ -684,7 +696,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -988,7 +1000,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Y86"/>
+  <dimension ref="A1:Y88"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
@@ -5341,14 +5353,14 @@
     </row>
     <row r="75" spans="1:24" x14ac:dyDescent="0.25">
       <c r="C75">
-        <f t="shared" ref="C75:C86" si="8">C74+1</f>
+        <f t="shared" ref="C75:C88" si="8">C74+1</f>
         <v>74</v>
       </c>
       <c r="D75" t="s">
         <v>152</v>
       </c>
       <c r="E75" t="str">
-        <f t="shared" ref="E75:E80" si="9">TEXT(C75,"00") &amp; " GICS-"&amp;K75&amp;" ("&amp;Q75&amp;IF(P75&lt;&gt;"","+ ","")&amp;P75&amp;")"</f>
+        <f t="shared" ref="E75:E82" si="9">TEXT(C75,"00") &amp; " GICS-"&amp;K75&amp;" ("&amp;Q75&amp;IF(P75&lt;&gt;"","+ ","")&amp;P75&amp;")"</f>
         <v>74 GICS-beta2m (beta3m)</v>
       </c>
       <c r="F75" t="s">
@@ -5519,87 +5531,87 @@
         <v>161</v>
       </c>
     </row>
-    <row r="78" spans="1:24" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="9" t="s">
+    <row r="78" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
         <v>23</v>
       </c>
-      <c r="B78" s="9" t="s">
+      <c r="B78" t="s">
         <v>23</v>
       </c>
-      <c r="C78" s="9">
+      <c r="C78">
         <f t="shared" si="8"/>
         <v>77</v>
       </c>
       <c r="D78" s="12" t="s">
         <v>170</v>
       </c>
-      <c r="E78" s="9" t="str">
-        <f t="shared" si="9"/>
+      <c r="E78" t="str">
+        <f t="shared" ref="E78:E79" si="10">TEXT(C78,"00") &amp; " GICS-"&amp;K78&amp;" ("&amp;Q78&amp;IF(P78&lt;&gt;"","+ ","")&amp;P78&amp;")"</f>
         <v>77 GICS-sh3m (beta3m)</v>
       </c>
-      <c r="F78" s="9" t="s">
-        <v>164</v>
-      </c>
-      <c r="G78" s="9" t="s">
+      <c r="F78" t="s">
+        <v>175</v>
+      </c>
+      <c r="G78" t="s">
         <v>25</v>
       </c>
-      <c r="H78" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="K78" s="9" t="s">
+      <c r="H78" t="s">
+        <v>26</v>
+      </c>
+      <c r="K78" t="s">
         <v>34</v>
       </c>
-      <c r="L78" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="M78" s="9">
-        <v>0.1</v>
-      </c>
-      <c r="N78" s="9">
-        <v>10</v>
-      </c>
-      <c r="O78" s="9">
-        <v>3</v>
-      </c>
-      <c r="Q78" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="R78" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="S78" s="9">
-        <v>1</v>
-      </c>
-      <c r="T78" s="9">
-        <v>3</v>
-      </c>
-      <c r="U78" s="9">
-        <v>0</v>
-      </c>
-      <c r="V78" s="9">
-        <v>20</v>
-      </c>
-      <c r="W78" s="9">
-        <v>0</v>
-      </c>
-      <c r="X78" s="9" t="s">
+      <c r="L78" t="s">
+        <v>28</v>
+      </c>
+      <c r="M78">
+        <v>0.1</v>
+      </c>
+      <c r="N78">
+        <v>10</v>
+      </c>
+      <c r="O78">
+        <v>3</v>
+      </c>
+      <c r="Q78" t="s">
+        <v>27</v>
+      </c>
+      <c r="R78" t="s">
+        <v>28</v>
+      </c>
+      <c r="S78">
+        <v>1</v>
+      </c>
+      <c r="T78">
+        <v>3</v>
+      </c>
+      <c r="U78">
+        <v>0</v>
+      </c>
+      <c r="V78">
+        <v>20</v>
+      </c>
+      <c r="W78">
+        <v>0</v>
+      </c>
+      <c r="X78" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="79" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>23</v>
+      </c>
       <c r="C79">
         <f t="shared" si="8"/>
         <v>78</v>
       </c>
-      <c r="D79" t="s">
-        <v>165</v>
-      </c>
       <c r="E79" t="str">
-        <f t="shared" si="9"/>
-        <v>78 GICS-beta3m (sh3m)</v>
+        <f t="shared" si="10"/>
+        <v>78 GICS-sh3m (beta3m+ Longi.sh3m&gt;0)</v>
       </c>
       <c r="F79" t="s">
-        <v>166</v>
+        <v>176</v>
       </c>
       <c r="G79" t="s">
         <v>25</v>
@@ -5608,7 +5620,7 @@
         <v>26</v>
       </c>
       <c r="K79" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="L79" t="s">
         <v>28</v>
@@ -5622,8 +5634,11 @@
       <c r="O79">
         <v>4</v>
       </c>
+      <c r="P79" t="s">
+        <v>173</v>
+      </c>
       <c r="Q79" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="R79" t="s">
         <v>28</v>
@@ -5648,19 +5663,19 @@
       </c>
     </row>
     <row r="80" spans="1:24" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A80" s="9" t="s">
+        <v>23</v>
+      </c>
       <c r="C80" s="9">
-        <f t="shared" si="8"/>
-        <v>79</v>
-      </c>
-      <c r="D80" s="9" t="s">
-        <v>165</v>
+        <f>C77+1</f>
+        <v>77</v>
       </c>
       <c r="E80" s="9" t="str">
         <f t="shared" si="9"/>
-        <v>79 GICS-sh3m (sh3m)</v>
+        <v>77 GICS-sh3m (beta3m+ Longi.sh3m&gt;2)</v>
       </c>
       <c r="F80" s="9" t="s">
-        <v>166</v>
+        <v>175</v>
       </c>
       <c r="G80" s="9" t="s">
         <v>25</v>
@@ -5683,8 +5698,11 @@
       <c r="O80" s="9">
         <v>4</v>
       </c>
+      <c r="P80" s="9" t="s">
+        <v>174</v>
+      </c>
       <c r="Q80" s="9" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="R80" s="9" t="s">
         <v>28</v>
@@ -5711,20 +5729,20 @@
     <row r="81" spans="3:24" x14ac:dyDescent="0.25">
       <c r="C81">
         <f t="shared" si="8"/>
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D81" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="E81" t="str">
-        <f t="shared" ref="E81:E86" si="10">TEXT(C81,"00") &amp; " Sector2-"&amp;K81&amp;" ("&amp;Q81&amp;IF(P81&lt;&gt;"","+ ","")&amp;P81&amp;")"</f>
-        <v>80 Sector2-beta3m (beta3m+ Longi.beta3m&gt;2)</v>
+        <f t="shared" si="9"/>
+        <v>78 GICS-beta3m (sh3m)</v>
       </c>
       <c r="F81" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="G81" t="s">
-        <v>156</v>
+        <v>25</v>
       </c>
       <c r="H81" t="s">
         <v>26</v>
@@ -5744,11 +5762,8 @@
       <c r="O81">
         <v>4</v>
       </c>
-      <c r="P81" t="s">
-        <v>163</v>
-      </c>
       <c r="Q81" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="R81" t="s">
         <v>28</v>
@@ -5772,78 +5787,81 @@
         <v>161</v>
       </c>
     </row>
-    <row r="82" spans="3:24" x14ac:dyDescent="0.25">
-      <c r="C82">
+    <row r="82" spans="3:24" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="C82" s="9">
         <f t="shared" si="8"/>
-        <v>81</v>
-      </c>
-      <c r="E82" t="str">
-        <f t="shared" si="10"/>
-        <v>81 Sector2-quot2050 (beta3m+ Longi.beta3m&gt;2)</v>
-      </c>
-      <c r="F82" t="s">
-        <v>158</v>
-      </c>
-      <c r="G82" t="s">
-        <v>156</v>
-      </c>
-      <c r="H82" t="s">
-        <v>26</v>
-      </c>
-      <c r="K82" t="s">
-        <v>45</v>
-      </c>
-      <c r="L82" t="s">
-        <v>28</v>
-      </c>
-      <c r="M82">
-        <v>0.1</v>
-      </c>
-      <c r="N82">
-        <v>10</v>
-      </c>
-      <c r="O82">
-        <v>4</v>
-      </c>
-      <c r="P82" t="s">
-        <v>163</v>
-      </c>
-      <c r="Q82" t="s">
-        <v>27</v>
-      </c>
-      <c r="R82" t="s">
-        <v>28</v>
-      </c>
-      <c r="S82">
-        <v>1</v>
-      </c>
-      <c r="T82">
-        <v>3</v>
-      </c>
-      <c r="U82">
-        <v>0</v>
-      </c>
-      <c r="V82">
-        <v>20</v>
-      </c>
-      <c r="W82">
-        <v>0</v>
-      </c>
-      <c r="X82" t="s">
-        <v>135</v>
+        <v>79</v>
+      </c>
+      <c r="D82" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="E82" s="9" t="str">
+        <f t="shared" si="9"/>
+        <v>79 GICS-sh3m (sh3m)</v>
+      </c>
+      <c r="F82" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="G82" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="H82" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="K82" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="L82" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="M82" s="9">
+        <v>0.1</v>
+      </c>
+      <c r="N82" s="9">
+        <v>10</v>
+      </c>
+      <c r="O82" s="9">
+        <v>4</v>
+      </c>
+      <c r="Q82" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="R82" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="S82" s="9">
+        <v>1</v>
+      </c>
+      <c r="T82" s="9">
+        <v>3</v>
+      </c>
+      <c r="U82" s="9">
+        <v>0</v>
+      </c>
+      <c r="V82" s="9">
+        <v>20</v>
+      </c>
+      <c r="W82" s="9">
+        <v>0</v>
+      </c>
+      <c r="X82" s="9" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="83" spans="3:24" x14ac:dyDescent="0.25">
       <c r="C83">
         <f t="shared" si="8"/>
-        <v>82</v>
+        <v>80</v>
+      </c>
+      <c r="D83" t="s">
+        <v>171</v>
       </c>
       <c r="E83" t="str">
-        <f t="shared" si="10"/>
-        <v>82 Sector2-beta3m (beta3m)</v>
+        <f t="shared" ref="E83:E88" si="11">TEXT(C83,"00") &amp; " Sector2-"&amp;K83&amp;" ("&amp;Q83&amp;IF(P83&lt;&gt;"","+ ","")&amp;P83&amp;")"</f>
+        <v>80 Sector2-beta3m (beta3m+ Longi.beta3m&gt;2)</v>
       </c>
       <c r="F83" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="G83" t="s">
         <v>156</v>
@@ -5866,6 +5884,9 @@
       <c r="O83">
         <v>4</v>
       </c>
+      <c r="P83" t="s">
+        <v>163</v>
+      </c>
       <c r="Q83" t="s">
         <v>27</v>
       </c>
@@ -5888,17 +5909,17 @@
         <v>0</v>
       </c>
       <c r="X83" t="s">
-        <v>135</v>
+        <v>161</v>
       </c>
     </row>
     <row r="84" spans="3:24" x14ac:dyDescent="0.25">
       <c r="C84">
         <f t="shared" si="8"/>
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E84" t="str">
-        <f t="shared" si="10"/>
-        <v>83 Sector2-quot2050 (beta3m)</v>
+        <f t="shared" si="11"/>
+        <v>81 Sector2-quot2050 (beta3m+ Longi.beta3m&gt;2)</v>
       </c>
       <c r="F84" t="s">
         <v>158</v>
@@ -5923,6 +5944,9 @@
       </c>
       <c r="O84">
         <v>4</v>
+      </c>
+      <c r="P84" t="s">
+        <v>163</v>
       </c>
       <c r="Q84" t="s">
         <v>27</v>
@@ -5952,17 +5976,14 @@
     <row r="85" spans="3:24" x14ac:dyDescent="0.25">
       <c r="C85">
         <f t="shared" si="8"/>
-        <v>84</v>
-      </c>
-      <c r="D85" t="s">
-        <v>172</v>
+        <v>82</v>
       </c>
       <c r="E85" t="str">
-        <f t="shared" si="10"/>
-        <v>84 Sector2-sh3m (beta3m+ Longi.beta3m&gt;2)</v>
+        <f t="shared" si="11"/>
+        <v>82 Sector2-beta3m (beta3m)</v>
       </c>
       <c r="F85" t="s">
-        <v>167</v>
+        <v>157</v>
       </c>
       <c r="G85" t="s">
         <v>156</v>
@@ -5971,7 +5992,7 @@
         <v>26</v>
       </c>
       <c r="K85" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="L85" t="s">
         <v>28</v>
@@ -5984,9 +6005,6 @@
       </c>
       <c r="O85">
         <v>4</v>
-      </c>
-      <c r="P85" t="s">
-        <v>163</v>
       </c>
       <c r="Q85" t="s">
         <v>27</v>
@@ -6013,66 +6031,189 @@
         <v>135</v>
       </c>
     </row>
-    <row r="86" spans="3:24" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="C86" s="9">
+    <row r="86" spans="3:24" x14ac:dyDescent="0.25">
+      <c r="C86">
+        <f t="shared" si="8"/>
+        <v>83</v>
+      </c>
+      <c r="E86" t="str">
+        <f t="shared" si="11"/>
+        <v>83 Sector2-quot2050 (beta3m)</v>
+      </c>
+      <c r="F86" t="s">
+        <v>158</v>
+      </c>
+      <c r="G86" t="s">
+        <v>156</v>
+      </c>
+      <c r="H86" t="s">
+        <v>26</v>
+      </c>
+      <c r="K86" t="s">
+        <v>45</v>
+      </c>
+      <c r="L86" t="s">
+        <v>28</v>
+      </c>
+      <c r="M86">
+        <v>0.1</v>
+      </c>
+      <c r="N86">
+        <v>10</v>
+      </c>
+      <c r="O86">
+        <v>4</v>
+      </c>
+      <c r="Q86" t="s">
+        <v>27</v>
+      </c>
+      <c r="R86" t="s">
+        <v>28</v>
+      </c>
+      <c r="S86">
+        <v>1</v>
+      </c>
+      <c r="T86">
+        <v>3</v>
+      </c>
+      <c r="U86">
+        <v>0</v>
+      </c>
+      <c r="V86">
+        <v>20</v>
+      </c>
+      <c r="W86">
+        <v>0</v>
+      </c>
+      <c r="X86" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="87" spans="3:24" x14ac:dyDescent="0.25">
+      <c r="C87">
+        <f t="shared" si="8"/>
+        <v>84</v>
+      </c>
+      <c r="D87" t="s">
+        <v>172</v>
+      </c>
+      <c r="E87" t="str">
+        <f t="shared" si="11"/>
+        <v>84 Sector2-sh3m (beta3m+ Longi.beta3m&gt;2)</v>
+      </c>
+      <c r="F87" t="s">
+        <v>167</v>
+      </c>
+      <c r="G87" t="s">
+        <v>156</v>
+      </c>
+      <c r="H87" t="s">
+        <v>26</v>
+      </c>
+      <c r="K87" t="s">
+        <v>34</v>
+      </c>
+      <c r="L87" t="s">
+        <v>28</v>
+      </c>
+      <c r="M87">
+        <v>0.1</v>
+      </c>
+      <c r="N87">
+        <v>10</v>
+      </c>
+      <c r="O87">
+        <v>4</v>
+      </c>
+      <c r="P87" t="s">
+        <v>163</v>
+      </c>
+      <c r="Q87" t="s">
+        <v>27</v>
+      </c>
+      <c r="R87" t="s">
+        <v>28</v>
+      </c>
+      <c r="S87">
+        <v>1</v>
+      </c>
+      <c r="T87">
+        <v>3</v>
+      </c>
+      <c r="U87">
+        <v>0</v>
+      </c>
+      <c r="V87">
+        <v>20</v>
+      </c>
+      <c r="W87">
+        <v>0</v>
+      </c>
+      <c r="X87" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="88" spans="3:24" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="C88" s="9">
         <f t="shared" si="8"/>
         <v>85</v>
       </c>
-      <c r="E86" s="9" t="str">
-        <f t="shared" si="10"/>
+      <c r="E88" s="9" t="str">
+        <f t="shared" si="11"/>
         <v>85 Sector2-sh3m (beta3m)</v>
       </c>
-      <c r="F86" s="9" t="s">
+      <c r="F88" s="9" t="s">
         <v>159</v>
       </c>
-      <c r="G86" s="9" t="s">
+      <c r="G88" s="9" t="s">
         <v>156</v>
       </c>
-      <c r="H86" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="K86" s="9" t="s">
+      <c r="H88" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="K88" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="L86" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="M86" s="9">
-        <v>0.1</v>
-      </c>
-      <c r="N86" s="9">
-        <v>10</v>
-      </c>
-      <c r="O86" s="9">
-        <v>4</v>
-      </c>
-      <c r="Q86" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="R86" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="S86" s="9">
-        <v>1</v>
-      </c>
-      <c r="T86" s="9">
-        <v>3</v>
-      </c>
-      <c r="U86" s="9">
-        <v>0</v>
-      </c>
-      <c r="V86" s="9">
-        <v>20</v>
-      </c>
-      <c r="W86" s="9">
-        <v>0</v>
-      </c>
-      <c r="X86" s="9" t="s">
+      <c r="L88" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="M88" s="9">
+        <v>0.1</v>
+      </c>
+      <c r="N88" s="9">
+        <v>10</v>
+      </c>
+      <c r="O88" s="9">
+        <v>4</v>
+      </c>
+      <c r="Q88" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="R88" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="S88" s="9">
+        <v>1</v>
+      </c>
+      <c r="T88" s="9">
+        <v>3</v>
+      </c>
+      <c r="U88" s="9">
+        <v>0</v>
+      </c>
+      <c r="V88" s="9">
+        <v>20</v>
+      </c>
+      <c r="W88" s="9">
+        <v>0</v>
+      </c>
+      <c r="X88" s="9" t="s">
         <v>161</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/strategy_grp2/app/control/control_board.xlsx
+++ b/strategy_grp2/app/control/control_board.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\Gandalf\sm-home\potentials\strategy_grp2\app\control\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{911DFE23-D83A-4E29-82A1-58B24BEDC6CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{234892A2-60B3-4734-A2E1-A0D246C78EDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="1665" windowWidth="28770" windowHeight="13965" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2115" yWindow="1050" windowWidth="26505" windowHeight="14190" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Runs" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="882" uniqueCount="177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="880" uniqueCount="177">
   <si>
     <t>D</t>
   </si>
@@ -5599,9 +5599,6 @@
       </c>
     </row>
     <row r="79" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A79" t="s">
-        <v>23</v>
-      </c>
       <c r="C79">
         <f t="shared" si="8"/>
         <v>78</v>
@@ -5663,9 +5660,6 @@
       </c>
     </row>
     <row r="80" spans="1:24" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="9" t="s">
-        <v>23</v>
-      </c>
       <c r="C80" s="9">
         <f>C77+1</f>
         <v>77</v>

--- a/strategy_grp2/app/control/control_board.xlsx
+++ b/strategy_grp2/app/control/control_board.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\Gandalf\sm-home\potentials\strategy_grp2\app\control\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{234892A2-60B3-4734-A2E1-A0D246C78EDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9C7AAA3-EEB5-405A-96D4-9499EE2EA584}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2115" yWindow="1050" windowWidth="26505" windowHeight="14190" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="2565" windowWidth="34695" windowHeight="14160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Runs" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="880" uniqueCount="177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="884" uniqueCount="177">
   <si>
     <t>D</t>
   </si>
@@ -1091,6 +1091,9 @@
       </c>
     </row>
     <row r="2" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>23</v>
+      </c>
       <c r="C2">
         <v>1</v>
       </c>
@@ -1141,7 +1144,7 @@
         <v>3</v>
       </c>
       <c r="U2">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="V2">
         <v>20</v>
@@ -1392,6 +1395,9 @@
       </c>
     </row>
     <row r="7" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>23</v>
+      </c>
       <c r="C7">
         <f t="shared" si="3"/>
         <v>6</v>
@@ -1437,7 +1443,7 @@
         <v>3</v>
       </c>
       <c r="U7">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="V7">
         <v>20</v>
@@ -5586,7 +5592,7 @@
         <v>3</v>
       </c>
       <c r="U78">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="V78">
         <v>20</v>
@@ -5720,7 +5726,10 @@
         <v>161</v>
       </c>
     </row>
-    <row r="81" spans="3:24" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>23</v>
+      </c>
       <c r="C81">
         <f t="shared" si="8"/>
         <v>78</v>
@@ -5769,7 +5778,7 @@
         <v>3</v>
       </c>
       <c r="U81">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="V81">
         <v>20</v>
@@ -5781,7 +5790,10 @@
         <v>161</v>
       </c>
     </row>
-    <row r="82" spans="3:24" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:24" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A82" s="9" t="s">
+        <v>23</v>
+      </c>
       <c r="C82" s="9">
         <f t="shared" si="8"/>
         <v>79</v>
@@ -5830,7 +5842,7 @@
         <v>3</v>
       </c>
       <c r="U82" s="9">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="V82" s="9">
         <v>20</v>
@@ -5842,7 +5854,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="83" spans="3:24" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:24" x14ac:dyDescent="0.25">
       <c r="C83">
         <f t="shared" si="8"/>
         <v>80</v>
@@ -5906,7 +5918,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="84" spans="3:24" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:24" x14ac:dyDescent="0.25">
       <c r="C84">
         <f t="shared" si="8"/>
         <v>81</v>
@@ -5967,7 +5979,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="85" spans="3:24" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:24" x14ac:dyDescent="0.25">
       <c r="C85">
         <f t="shared" si="8"/>
         <v>82</v>
@@ -6025,7 +6037,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="86" spans="3:24" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:24" x14ac:dyDescent="0.25">
       <c r="C86">
         <f t="shared" si="8"/>
         <v>83</v>
@@ -6083,7 +6095,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="87" spans="3:24" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:24" x14ac:dyDescent="0.25">
       <c r="C87">
         <f t="shared" si="8"/>
         <v>84</v>
@@ -6147,7 +6159,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="88" spans="3:24" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:24" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C88" s="9">
         <f t="shared" si="8"/>
         <v>85</v>
